--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FBEFA7B-DA9C-4DF9-9E08-E321DE12163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADD9032-688B-456F-BFCF-8FFB91034E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -879,10 +879,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-10}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopRecure",percent:10}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1043,6 +1039,10 @@
   </si>
   <si>
     <t>[{class:"TroopSetDamage", value:0,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-20}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1605,22 +1605,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1635,7 +1635,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1648,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1675,7 +1675,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>211</v>
@@ -1704,7 +1704,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1758,7 +1758,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1785,7 +1785,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1812,7 +1812,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1839,7 +1839,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1866,7 +1866,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1985,10 +1985,10 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -2103,12 +2103,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="28">
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>48</v>
@@ -2129,7 +2129,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2176,12 +2176,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="28">
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>54</v>
@@ -2197,10 +2197,10 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="28">
         <v>23</v>
       </c>
@@ -2265,10 +2265,10 @@
         <v>35</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="28">
         <v>24</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="28">
         <v>25</v>
       </c>
@@ -2317,15 +2317,15 @@
         <v>35</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="28">
         <v>26</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D30" s="28" t="s">
         <v>65</v>
@@ -2343,10 +2343,10 @@
         <v>35</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B32" s="28">
         <v>28</v>
       </c>
@@ -2388,10 +2388,10 @@
         <v>70</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B33" s="28">
         <v>29</v>
       </c>
@@ -2412,10 +2412,10 @@
         <v>70</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B37" s="28">
         <v>33</v>
       </c>
@@ -2499,10 +2499,10 @@
         <v>70</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B38" s="28">
         <v>34</v>
       </c>
@@ -2523,10 +2523,10 @@
         <v>70</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="14">
         <v>36</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="14">
         <v>37</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="14">
         <v>38</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="14">
         <v>39</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="14">
         <v>40</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="14">
         <v>41</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="14">
         <v>42</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="14">
         <v>43</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="14">
         <v>44</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="14">
         <v>45</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="14">
         <v>46</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="14">
         <v>47</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="14">
         <v>48</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="14">
         <v>49</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="28">
         <v>50</v>
       </c>
@@ -2939,10 +2939,10 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>49</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="28">
         <v>55</v>
       </c>
@@ -3056,10 +3056,10 @@
         <v>49</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B60" s="28">
         <v>56</v>
       </c>
@@ -3082,10 +3082,10 @@
         <v>49</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="28">
         <v>57</v>
       </c>
@@ -3108,10 +3108,10 @@
         <v>49</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="28">
         <v>58</v>
       </c>
@@ -3134,10 +3134,10 @@
         <v>49</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="28">
         <v>59</v>
       </c>
@@ -3160,10 +3160,10 @@
         <v>49</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B64" s="28">
         <v>60</v>
       </c>
@@ -3186,10 +3186,10 @@
         <v>49</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B65" s="28">
         <v>61</v>
       </c>
@@ -3212,10 +3212,10 @@
         <v>49</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="14">
         <v>62</v>
       </c>
@@ -3238,13 +3238,13 @@
         <v>49</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J66" s="15" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="28">
         <v>63</v>
       </c>
@@ -3267,10 +3267,10 @@
         <v>49</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B68" s="28">
         <v>64</v>
       </c>
@@ -3293,10 +3293,10 @@
         <v>49</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="28">
         <v>65</v>
       </c>
@@ -3319,10 +3319,10 @@
         <v>49</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B70" s="28">
         <v>66</v>
       </c>
@@ -3345,10 +3345,10 @@
         <v>49</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
       <c r="B71" s="28">
         <v>67</v>
       </c>
@@ -3369,15 +3369,15 @@
         <v>49</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="28">
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>146</v>
@@ -3395,10 +3395,10 @@
         <v>49</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3482,12 +3482,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B77" s="28">
         <v>73</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>154</v>
@@ -3505,10 +3505,10 @@
         <v>155</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="28">
         <v>74</v>
       </c>
@@ -3531,15 +3531,15 @@
         <v>155</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="28">
         <v>75</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>158</v>
@@ -3557,10 +3557,10 @@
         <v>155</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="14">
         <v>80</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="14">
         <v>81</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="14">
         <v>82</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="14">
         <v>84</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="9">
         <v>100</v>
       </c>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EADD9032-688B-456F-BFCF-8FFB91034E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32E3E03-32ED-45B1-86BE-E89FC2942031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -979,14 +979,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{class:"AddBuff",buffId:1,probability:10000,values:[1,2], weight:[70,30],
-condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:0}] }
-},{class:"AddBuff",buffId:1,probability:10000,values:[2,3], weight:[70,30],
-condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:1}] }
-}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hasInit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1043,6 +1035,14 @@
   </si>
   <si>
     <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-20}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[1,2], weight:[70,30],
+condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:0}] }
+},{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[2,3], weight:[70,30],
+condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:1}] }
+}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1689,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>211</v>
@@ -1985,7 +1985,7 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
@@ -2181,7 +2181,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>54</v>
@@ -2197,7 +2197,7 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.15">
@@ -2388,7 +2388,7 @@
         <v>70</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2412,7 +2412,7 @@
         <v>70</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.15">
@@ -2499,7 +2499,7 @@
         <v>70</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2523,7 +2523,7 @@
         <v>70</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2939,7 +2939,7 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3369,7 +3369,7 @@
         <v>49</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A32E3E03-32ED-45B1-86BE-E89FC2942031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5770761-FF0C-4784-BB3B-E5394B0BF9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -867,10 +867,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{"class": "TroopComboAttack","count": 1,"condition": {"class": "andList","list": [{"class": "SkillIsNormalSkill","result": 1}]},"comboCondition": {"class": "andList","list": [{"class": "ProbabilityCheck","probability": 5000}]}}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:1}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1038,7 +1034,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillRenderEnd"}],"actionList":[{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[1,2], weight:[70,30],
+    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillActionEnd"}],"actionList":[{"class": "TroopComboAttack","count": 1,"condition": {"class": "andList","list": [{"class": "SkillIsNormalSkill","result": 1}]},"comboCondition": {"class": "andList","list": [{"class": "ProbabilityCheck","probability": 5000}]}}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillActionEnd"}],"actionList":[{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[1,2], weight:[70,30],
 condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:0}] }
 },{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[2,3], weight:[70,30],
 condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:1}] }
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1689,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>211</v>
@@ -1959,7 +1959,7 @@
         <v>35</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -1985,7 +1985,7 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
@@ -2032,7 +2032,7 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.15">
@@ -2108,7 +2108,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>48</v>
@@ -2181,7 +2181,7 @@
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>54</v>
@@ -2197,7 +2197,7 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.15">
@@ -2265,7 +2265,7 @@
         <v>35</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2291,7 +2291,7 @@
         <v>35</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2317,7 +2317,7 @@
         <v>35</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2325,7 +2325,7 @@
         <v>26</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D30" s="28" t="s">
         <v>65</v>
@@ -2343,7 +2343,7 @@
         <v>35</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.15">
@@ -2388,7 +2388,7 @@
         <v>70</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2412,7 +2412,7 @@
         <v>70</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.15">
@@ -2499,7 +2499,7 @@
         <v>70</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2523,7 +2523,7 @@
         <v>70</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3030,7 +3030,7 @@
         <v>49</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3056,7 +3056,7 @@
         <v>49</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3082,7 +3082,7 @@
         <v>49</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3108,7 +3108,7 @@
         <v>49</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3134,7 +3134,7 @@
         <v>49</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3160,7 +3160,7 @@
         <v>49</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3186,7 +3186,7 @@
         <v>49</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3212,7 +3212,7 @@
         <v>49</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3238,7 +3238,7 @@
         <v>49</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J66" s="15" t="s">
         <v>222</v>
@@ -3267,7 +3267,7 @@
         <v>49</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3293,7 +3293,7 @@
         <v>49</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3319,7 +3319,7 @@
         <v>49</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3345,7 +3345,7 @@
         <v>49</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
@@ -3369,7 +3369,7 @@
         <v>49</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3377,7 +3377,7 @@
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>146</v>
@@ -3395,7 +3395,7 @@
         <v>49</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.15">
@@ -3487,7 +3487,7 @@
         <v>73</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>154</v>
@@ -3505,7 +3505,7 @@
         <v>155</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3531,7 +3531,7 @@
         <v>155</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3539,7 +3539,7 @@
         <v>75</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>158</v>
@@ -3557,7 +3557,7 @@
         <v>155</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.15">

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5770761-FF0C-4784-BB3B-E5394B0BF9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CBB78B-C6E0-4B3A-9CD9-947E411B30D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -1022,14 +1022,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSetDamage", value:0,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-20}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1043,6 +1035,14 @@
 },{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[2,3], weight:[70,30],
 condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:1}] }
 }]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:-1,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:-1,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1605,22 +1605,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1635,7 +1635,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1648,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1758,7 +1758,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1785,7 +1785,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1812,7 +1812,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1839,7 +1839,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1866,7 +1866,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1985,10 +1985,10 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2032,10 +2032,10 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28">
         <v>17</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="28">
         <v>20</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="28">
         <v>23</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="28">
         <v>24</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="28">
         <v>25</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="28">
         <v>26</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="28">
         <v>28</v>
       </c>
@@ -2388,10 +2388,10 @@
         <v>70</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28">
         <v>29</v>
       </c>
@@ -2412,10 +2412,10 @@
         <v>70</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="28">
         <v>33</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="28">
         <v>34</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <v>36</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <v>37</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="14">
         <v>38</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <v>39</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <v>40</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <v>41</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <v>42</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <v>43</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <v>44</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <v>45</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <v>46</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <v>47</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <v>48</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <v>49</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="28">
         <v>50</v>
       </c>
@@ -2939,10 +2939,10 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28">
         <v>55</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28">
         <v>56</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="28">
         <v>57</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="28">
         <v>58</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="28">
         <v>59</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="28">
         <v>60</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28">
         <v>61</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="14">
         <v>62</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="28">
         <v>63</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="28">
         <v>64</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="28">
         <v>65</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="28">
         <v>66</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
       <c r="B71" s="28">
         <v>67</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="28">
         <v>68</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="28">
         <v>73</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="28">
         <v>74</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="28">
         <v>75</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="14">
         <v>80</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="14">
         <v>81</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="14">
         <v>82</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14">
         <v>84</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="9">
         <v>100</v>
       </c>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66CBB78B-C6E0-4B3A-9CD9-947E411B30D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1CF4A6-8BBA-4EDA-B043-1E228D67C1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3870" yWindow="2715" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -883,10 +883,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1043,6 +1039,10 @@
   </si>
   <si>
     <t>[{class:"TroopSetDamage", value:-1,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddSkillAttackRange", "atkType":5,"addRange":1,condition:{{class:"SkillIdInList", ids:[22], result:1}}},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1605,22 +1605,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1635,7 +1635,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1648,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1675,7 +1675,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>211</v>
@@ -1704,7 +1704,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1758,7 +1758,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1785,7 +1785,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1812,7 +1812,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1839,7 +1839,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1866,7 +1866,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1985,10 +1985,10 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2032,10 +2032,10 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -2103,12 +2103,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="28">
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>48</v>
@@ -2129,7 +2129,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2176,12 +2176,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="28">
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>54</v>
@@ -2197,10 +2197,10 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="28">
         <v>23</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="28">
         <v>24</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="28">
         <v>25</v>
       </c>
@@ -2317,15 +2317,15 @@
         <v>35</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="28">
         <v>26</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D30" s="28" t="s">
         <v>65</v>
@@ -2343,10 +2343,10 @@
         <v>35</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B32" s="28">
         <v>28</v>
       </c>
@@ -2388,10 +2388,10 @@
         <v>70</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B33" s="28">
         <v>29</v>
       </c>
@@ -2412,10 +2412,10 @@
         <v>70</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B37" s="28">
         <v>33</v>
       </c>
@@ -2499,10 +2499,10 @@
         <v>70</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B38" s="28">
         <v>34</v>
       </c>
@@ -2523,10 +2523,10 @@
         <v>70</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="14">
         <v>36</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="14">
         <v>37</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="14">
         <v>38</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="14">
         <v>39</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="14">
         <v>40</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="14">
         <v>41</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="14">
         <v>42</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="14">
         <v>43</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="14">
         <v>44</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="14">
         <v>45</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="14">
         <v>46</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="14">
         <v>47</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="14">
         <v>48</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="14">
         <v>49</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="28">
         <v>50</v>
       </c>
@@ -2939,10 +2939,10 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>49</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="28">
         <v>55</v>
       </c>
@@ -3056,10 +3056,10 @@
         <v>49</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B60" s="28">
         <v>56</v>
       </c>
@@ -3082,10 +3082,10 @@
         <v>49</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="28">
         <v>57</v>
       </c>
@@ -3108,10 +3108,10 @@
         <v>49</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="28">
         <v>58</v>
       </c>
@@ -3134,10 +3134,10 @@
         <v>49</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="28">
         <v>59</v>
       </c>
@@ -3160,10 +3160,10 @@
         <v>49</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B64" s="28">
         <v>60</v>
       </c>
@@ -3186,10 +3186,10 @@
         <v>49</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B65" s="28">
         <v>61</v>
       </c>
@@ -3212,10 +3212,10 @@
         <v>49</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="14">
         <v>62</v>
       </c>
@@ -3238,13 +3238,13 @@
         <v>49</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J66" s="15" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="28">
         <v>63</v>
       </c>
@@ -3267,10 +3267,10 @@
         <v>49</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B68" s="28">
         <v>64</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="28">
         <v>65</v>
       </c>
@@ -3319,10 +3319,10 @@
         <v>49</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B70" s="28">
         <v>66</v>
       </c>
@@ -3345,10 +3345,10 @@
         <v>49</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
       <c r="B71" s="28">
         <v>67</v>
       </c>
@@ -3369,15 +3369,15 @@
         <v>49</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="28">
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>146</v>
@@ -3395,10 +3395,10 @@
         <v>49</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3482,12 +3482,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B77" s="28">
         <v>73</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>154</v>
@@ -3505,10 +3505,10 @@
         <v>155</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="28">
         <v>74</v>
       </c>
@@ -3531,15 +3531,15 @@
         <v>155</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="28">
         <v>75</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>158</v>
@@ -3557,10 +3557,10 @@
         <v>155</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="14">
         <v>80</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="14">
         <v>81</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="14">
         <v>82</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="14">
         <v>84</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="9">
         <v>100</v>
       </c>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1CF4A6-8BBA-4EDA-B043-1E228D67C1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8004BBF5-554E-4D54-A2F8-8D92F3D1B7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3870" yWindow="2715" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -1042,7 +1042,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{class:"TroopAddSkillAttackRange", "atkType":5,"addRange":1,condition:{{class:"SkillIdInList", ids:[22], result:1}}},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
+    <t>[{class:"TroopAddSkillAttackRange", "atkType":5,"addRange":1,condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1605,22 +1605,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1635,7 +1635,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1648,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1758,7 +1758,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1785,7 +1785,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1812,7 +1812,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1839,7 +1839,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1866,7 +1866,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28">
         <v>17</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="28">
         <v>20</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="28">
         <v>23</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="28">
         <v>24</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="28">
         <v>25</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="28">
         <v>26</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="28">
         <v>28</v>
       </c>
@@ -2391,7 +2391,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28">
         <v>29</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="28">
         <v>33</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="28">
         <v>34</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <v>36</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <v>37</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="14">
         <v>38</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <v>39</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <v>40</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <v>41</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <v>42</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <v>43</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <v>44</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <v>45</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <v>46</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <v>47</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <v>48</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <v>49</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="28">
         <v>50</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28">
         <v>55</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28">
         <v>56</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="28">
         <v>57</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="28">
         <v>58</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="28">
         <v>59</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="28">
         <v>60</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28">
         <v>61</v>
       </c>
@@ -3215,7 +3215,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="14">
         <v>62</v>
       </c>
@@ -3244,7 +3244,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="28">
         <v>63</v>
       </c>
@@ -3270,7 +3270,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="28">
         <v>64</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="28">
         <v>65</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="28">
         <v>66</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
       <c r="B71" s="28">
         <v>67</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="28">
         <v>68</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="28">
         <v>73</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="28">
         <v>74</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="28">
         <v>75</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="9">
         <v>76</v>
       </c>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I80" s="20"/>
     </row>
-    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="9">
         <v>77</v>
       </c>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="I81" s="20"/>
     </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="14">
         <v>80</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="14">
         <v>81</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="14">
         <v>82</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14">
         <v>84</v>
       </c>
@@ -3778,7 +3778,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="9">
         <v>88</v>
       </c>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="9">
         <v>89</v>
       </c>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="9">
         <v>100</v>
       </c>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8004BBF5-554E-4D54-A2F8-8D92F3D1B7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398FDBD8-1585-482D-B9F1-11B37836C372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="3225" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="290">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -551,10 +551,6 @@
     <t>诗想</t>
   </si>
   <si>
-    <t>军乐台的回复气力效果增为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>筑城</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -972,10 +968,6 @@
   </si>
   <si>
     <t>hasInit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1043,6 +1035,18 @@
   </si>
   <si>
     <t>[{class:"TroopAddSkillAttackRange", "atkType":5,"addRange":1,condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerTroopTurnStart"}], actionList:[{class:"TroopChangeMorale",value:5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任何回复气力效果增为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerTroopOnMoralChange"}], actionList:[{class:"TroopModifyMorale",value:20000}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1605,22 +1609,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1635,7 +1639,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1648,7 +1652,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1662,7 +1666,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1672,10 +1676,10 @@
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="16" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1689,22 +1693,22 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>277</v>
+        <v>4</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1728,10 +1732,10 @@
         <v>16</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1755,10 +1759,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1782,10 +1786,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1809,10 +1813,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1836,10 +1840,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1863,10 +1867,10 @@
         <v>16</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1888,7 +1892,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1911,10 +1915,10 @@
         <v>16</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1936,7 +1940,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1959,10 +1963,10 @@
         <v>35</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1985,10 +1989,10 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2009,7 +2013,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2032,10 +2036,10 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>14</v>
       </c>
@@ -2056,7 +2060,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2077,7 +2081,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -2100,15 +2104,15 @@
         <v>35</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="28">
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>48</v>
@@ -2126,10 +2130,10 @@
         <v>49</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2152,10 +2156,10 @@
         <v>35</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2176,12 +2180,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="28">
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>54</v>
@@ -2197,10 +2201,10 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2221,7 +2225,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2242,7 +2246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="28">
         <v>23</v>
       </c>
@@ -2265,10 +2269,10 @@
         <v>35</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="28">
         <v>24</v>
       </c>
@@ -2291,10 +2295,10 @@
         <v>35</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="28">
         <v>25</v>
       </c>
@@ -2317,15 +2321,15 @@
         <v>35</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="28">
         <v>26</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D30" s="28" t="s">
         <v>65</v>
@@ -2343,10 +2347,10 @@
         <v>35</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2367,7 +2371,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B32" s="28">
         <v>28</v>
       </c>
@@ -2388,10 +2392,10 @@
         <v>70</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B33" s="28">
         <v>29</v>
       </c>
@@ -2412,10 +2416,10 @@
         <v>70</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2436,7 +2440,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2457,7 +2461,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2478,7 +2482,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B37" s="28">
         <v>33</v>
       </c>
@@ -2499,10 +2503,10 @@
         <v>70</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B38" s="28">
         <v>34</v>
       </c>
@@ -2523,10 +2527,10 @@
         <v>70</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -2549,10 +2553,10 @@
         <v>35</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="14">
         <v>36</v>
       </c>
@@ -2575,10 +2579,10 @@
         <v>35</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="14">
         <v>37</v>
       </c>
@@ -2601,10 +2605,10 @@
         <v>35</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="14">
         <v>38</v>
       </c>
@@ -2627,10 +2631,10 @@
         <v>35</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="14">
         <v>39</v>
       </c>
@@ -2653,10 +2657,10 @@
         <v>35</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="14">
         <v>40</v>
       </c>
@@ -2679,10 +2683,10 @@
         <v>35</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="14">
         <v>41</v>
       </c>
@@ -2705,10 +2709,10 @@
         <v>35</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="14">
         <v>42</v>
       </c>
@@ -2731,15 +2735,15 @@
         <v>35</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="14">
         <v>43</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>99</v>
@@ -2757,10 +2761,10 @@
         <v>35</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="14">
         <v>44</v>
       </c>
@@ -2783,10 +2787,10 @@
         <v>35</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="14">
         <v>45</v>
       </c>
@@ -2809,10 +2813,10 @@
         <v>35</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="14">
         <v>46</v>
       </c>
@@ -2835,10 +2839,10 @@
         <v>35</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="14">
         <v>47</v>
       </c>
@@ -2861,10 +2865,10 @@
         <v>35</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="14">
         <v>48</v>
       </c>
@@ -2887,10 +2891,10 @@
         <v>35</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="14">
         <v>49</v>
       </c>
@@ -2913,10 +2917,10 @@
         <v>35</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="28">
         <v>50</v>
       </c>
@@ -2939,10 +2943,10 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2964,7 +2968,7 @@
       </c>
       <c r="I55" s="20"/>
     </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -2986,7 +2990,7 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -3007,7 +3011,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3030,10 +3034,10 @@
         <v>49</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="28">
         <v>55</v>
       </c>
@@ -3056,10 +3060,10 @@
         <v>49</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B60" s="28">
         <v>56</v>
       </c>
@@ -3082,10 +3086,10 @@
         <v>49</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="28">
         <v>57</v>
       </c>
@@ -3108,10 +3112,10 @@
         <v>49</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="28">
         <v>58</v>
       </c>
@@ -3134,10 +3138,10 @@
         <v>49</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="28">
         <v>59</v>
       </c>
@@ -3160,10 +3164,10 @@
         <v>49</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B64" s="28">
         <v>60</v>
       </c>
@@ -3186,10 +3190,10 @@
         <v>49</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B65" s="28">
         <v>61</v>
       </c>
@@ -3212,10 +3216,10 @@
         <v>49</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="14">
         <v>62</v>
       </c>
@@ -3223,7 +3227,7 @@
         <v>135</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E66" s="28">
         <v>1</v>
@@ -3238,13 +3242,13 @@
         <v>49</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="28">
         <v>63</v>
       </c>
@@ -3267,10 +3271,10 @@
         <v>49</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B68" s="28">
         <v>64</v>
       </c>
@@ -3293,10 +3297,10 @@
         <v>49</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="28">
         <v>65</v>
       </c>
@@ -3319,10 +3323,10 @@
         <v>49</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B70" s="28">
         <v>66</v>
       </c>
@@ -3345,10 +3349,10 @@
         <v>49</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
       <c r="B71" s="28">
         <v>67</v>
       </c>
@@ -3369,15 +3373,15 @@
         <v>49</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="28">
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>146</v>
@@ -3395,10 +3399,10 @@
         <v>49</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3419,7 +3423,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3427,7 +3431,7 @@
         <v>149</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11">
@@ -3440,7 +3444,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3461,7 +3465,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3482,12 +3486,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B77" s="28">
         <v>73</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>154</v>
@@ -3505,10 +3509,10 @@
         <v>155</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="28">
         <v>74</v>
       </c>
@@ -3531,15 +3535,15 @@
         <v>155</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="28">
         <v>75</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>158</v>
@@ -3557,62 +3561,66 @@
         <v>155</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="9">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B80" s="14">
         <v>76</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="D80" s="9" t="s">
+      <c r="D80" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9">
+      <c r="E80" s="14"/>
+      <c r="F80" s="14">
         <v>3</v>
       </c>
-      <c r="G80" s="11">
+      <c r="G80" s="14">
         <v>5</v>
       </c>
-      <c r="H80" s="9" t="s">
+      <c r="H80" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="I80" s="20"/>
-    </row>
-    <row r="81" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="9">
+      <c r="I80" s="19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B81" s="14">
         <v>77</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9">
-        <v>2</v>
-      </c>
-      <c r="G81" s="11">
+      <c r="D81" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14">
+        <v>2</v>
+      </c>
+      <c r="G81" s="14">
         <v>5</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="H81" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="I81" s="20"/>
-    </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I81" s="19" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="9">
         <v>78</v>
       </c>
       <c r="C82" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="9">
@@ -3626,15 +3634,15 @@
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
       <c r="C83" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D83" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="E83" s="9"/>
       <c r="F83" s="9">
@@ -3648,16 +3656,16 @@
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="14">
         <v>80</v>
       </c>
       <c r="C84" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D84" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="D84" s="14" t="s">
-        <v>168</v>
-      </c>
       <c r="E84" s="14">
         <v>1</v>
       </c>
@@ -3665,25 +3673,25 @@
         <v>2</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H84" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="14">
         <v>81</v>
       </c>
       <c r="C85" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D85" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D85" s="14" t="s">
-        <v>170</v>
-      </c>
       <c r="E85" s="14">
         <v>1</v>
       </c>
@@ -3691,25 +3699,25 @@
         <v>2</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H85" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="14">
         <v>82</v>
       </c>
       <c r="C86" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D86" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D86" s="14" t="s">
-        <v>172</v>
-      </c>
       <c r="E86" s="14">
         <v>1</v>
       </c>
@@ -3717,16 +3725,16 @@
         <v>2</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H86" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3734,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E87" s="14">
         <v>1</v>
@@ -3743,25 +3751,25 @@
         <v>2</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H87" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="14">
         <v>84</v>
       </c>
       <c r="C88" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D88" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="D88" s="14" t="s">
-        <v>175</v>
-      </c>
       <c r="E88" s="14">
         <v>1</v>
       </c>
@@ -3769,46 +3777,46 @@
         <v>2</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H88" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I88" s="19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="9">
         <v>85</v>
       </c>
       <c r="C89" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D89" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="E89" s="9"/>
       <c r="F89" s="9">
         <v>2</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
       <c r="C90" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D90" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="E90" s="9"/>
       <c r="F90" s="9">
@@ -3822,15 +3830,15 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
       <c r="C91" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D91" s="9" t="s">
         <v>180</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="E91" s="9"/>
       <c r="F91" s="9">
@@ -3844,15 +3852,15 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B92" s="9">
         <v>88</v>
       </c>
       <c r="C92" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="E92" s="9"/>
       <c r="F92" s="9">
@@ -3862,19 +3870,19 @@
         <v>7</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="9">
         <v>89</v>
       </c>
       <c r="C93" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D93" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9">
@@ -3884,19 +3892,19 @@
         <v>7</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="9">
         <v>90</v>
       </c>
       <c r="C94" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9">
@@ -3906,19 +3914,19 @@
         <v>7</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="9">
         <v>91</v>
       </c>
       <c r="C95" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D95" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9">
@@ -3928,19 +3936,19 @@
         <v>7</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="9">
         <v>92</v>
       </c>
       <c r="C96" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D96" s="9" t="s">
         <v>191</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9">
@@ -3950,19 +3958,19 @@
         <v>8</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="9">
         <v>93</v>
       </c>
       <c r="C97" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="D97" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9">
@@ -3972,19 +3980,19 @@
         <v>8</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="9">
         <v>94</v>
       </c>
       <c r="C98" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D98" s="9" t="s">
         <v>196</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9">
@@ -3994,19 +4002,19 @@
         <v>8</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="9">
         <v>95</v>
       </c>
       <c r="C99" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D99" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>199</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9">
@@ -4016,19 +4024,19 @@
         <v>8</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="9">
         <v>96</v>
       </c>
       <c r="C100" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="E100" s="9"/>
       <c r="F100" s="9">
@@ -4038,19 +4046,19 @@
         <v>8</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="9">
         <v>97</v>
       </c>
       <c r="C101" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D101" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="E101" s="9"/>
       <c r="F101" s="9">
@@ -4060,19 +4068,19 @@
         <v>8</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="9">
         <v>98</v>
       </c>
       <c r="C102" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D102" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9">
@@ -4082,19 +4090,19 @@
         <v>8</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="9">
         <v>99</v>
       </c>
       <c r="C103" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D103" s="9" t="s">
         <v>206</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="E103" s="9"/>
       <c r="F103" s="9">
@@ -4104,19 +4112,19 @@
         <v>8</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="9">
         <v>100</v>
       </c>
       <c r="C104" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9">
@@ -4126,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I104" s="20"/>
     </row>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398FDBD8-1585-482D-B9F1-11B37836C372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFFEC01-3B49-4927-B5B8-3095CE4457ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="3225" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="296">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,824 +173,874 @@
     <t>施展一般攻击时，可连续攻击２次</t>
   </si>
   <si>
+    <t>于陆上攻击时，不会受到损伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强袭</t>
+  </si>
+  <si>
+    <t>于水上攻击时，不会受到损伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乱战</t>
+  </si>
+  <si>
+    <t>于森林中攻击时施展会心一击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伏兵成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>计略</t>
+  </si>
+  <si>
+    <t>攻城</t>
+  </si>
+  <si>
+    <t>攻击据点、设施、建筑物时施展会心一击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掎角</t>
+  </si>
+  <si>
+    <t>施展齐攻时，让对方陷入混乱</t>
+  </si>
+  <si>
+    <t>击破敌方部队时，必定可捕捉无特技「强运」或名马的敌将</t>
+  </si>
+  <si>
+    <t>精妙</t>
+  </si>
+  <si>
+    <t>击破敌方部队时所获得的技巧点数增为２倍</t>
+  </si>
+  <si>
+    <t>掠夺</t>
+  </si>
+  <si>
+    <t>击破敌方部队时，有机会夺取敌将的道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻心</t>
+  </si>
+  <si>
+    <t>攻击时可将敌方部队的一部分士兵吸收到自军部队中</t>
+  </si>
+  <si>
+    <t>驱逐</t>
+  </si>
+  <si>
+    <t>施展一般攻击时会心一击</t>
+  </si>
+  <si>
+    <t>射程</t>
+  </si>
+  <si>
+    <t>使井阑、投石的射程增加１区格</t>
+  </si>
+  <si>
+    <t>未研究技巧「骑射」时也可施展骑射；骑射可施展会心一击</t>
+  </si>
+  <si>
+    <t>辅佐</t>
+  </si>
+  <si>
+    <t>即使没建立人际关系（厌恶除外）也可获得支援攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不屈</t>
+  </si>
+  <si>
+    <t>若在部队的士兵不多时被攻击，不会受到损伤</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>金刚</t>
+  </si>
+  <si>
+    <t>在敌方攻击力微弱时被攻击的话，不会受到损伤</t>
+  </si>
+  <si>
+    <t>铁壁</t>
+  </si>
+  <si>
+    <t>就算被一齐攻击，也会视之为一般攻击</t>
+  </si>
+  <si>
+    <t>怒发</t>
+  </si>
+  <si>
+    <t>遭受敌方部队的战法攻击时，气力就会回复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤甲</t>
+  </si>
+  <si>
+    <t>强运</t>
+  </si>
+  <si>
+    <t>不会战死、被俘、负伤</t>
+  </si>
+  <si>
+    <t>血路</t>
+  </si>
+  <si>
+    <t>就算部队溃灭，同部队的武将也不会被俘虏</t>
+  </si>
+  <si>
+    <t>枪将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展枪兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>戟将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展戟兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>弓将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展弩兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>骑将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展骑兵战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>水将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展水军战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>勇将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展全战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>神将</t>
+  </si>
+  <si>
+    <t>对武力比自己低的敌方部队施展一般攻击及战法成功时会心一击</t>
+  </si>
+  <si>
+    <t>斗神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪兵战法与戟兵战法施展成功时会心一击</t>
+  </si>
+  <si>
+    <t>枪兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>戟神</t>
+  </si>
+  <si>
+    <t>戟兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>弓神</t>
+  </si>
+  <si>
+    <t>弩兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>骑神</t>
+  </si>
+  <si>
+    <t>骑兵战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>工神</t>
+  </si>
+  <si>
+    <t>兵器战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>水神</t>
+  </si>
+  <si>
+    <t>水军战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>霸王</t>
+  </si>
+  <si>
+    <t>全战法成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>疾驰</t>
+  </si>
+  <si>
+    <t>对攻击力比自部队低的敌方部队施展骑兵战法成功时，必使其陷入混乱</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>猛者</t>
+  </si>
+  <si>
+    <t>以战法让敌方部队移动区格时，可让敌将负伤</t>
+  </si>
+  <si>
+    <t>护卫</t>
+  </si>
+  <si>
+    <t>同部队的武将不会战死、负伤</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「火计」时必定会成功</t>
+  </si>
+  <si>
+    <t>言毒</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「伪报」时，必定会成功</t>
+  </si>
+  <si>
+    <t>机智</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「扰乱」时，必定会成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诡计</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略「内讧」时，必定会成功</t>
+  </si>
+  <si>
+    <t>虚实</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展全部队计略时，必定会成功</t>
+  </si>
+  <si>
+    <t>妙计</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展部队计略成功时会心一击</t>
+  </si>
+  <si>
+    <t>秘计</t>
+  </si>
+  <si>
+    <t>对智力比自己高的敌方部队施展部队计略成功时会心一击</t>
+  </si>
+  <si>
+    <t>看破</t>
+  </si>
+  <si>
+    <t>必定可识破智力比自己低的敌方部队所施展部队计略</t>
+  </si>
+  <si>
+    <t>洞察</t>
+  </si>
+  <si>
+    <t>火神</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展火计时必会成功；于全火攻有所优势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神算</t>
+  </si>
+  <si>
+    <t>对智力比自己低的敌方部队施展计略必会成功；于全计略有所优势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>百出</t>
+  </si>
+  <si>
+    <t>部队计略的消费气力减少</t>
+  </si>
+  <si>
+    <t>鬼谋</t>
+  </si>
+  <si>
+    <t>增广２区格可施展部队计略的范围</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>连环</t>
+  </si>
+  <si>
+    <t>部队计略成功时，与对象部队邻接的部队也会遭受计略波及</t>
+  </si>
+  <si>
+    <t>部队计略成功时施展会心一击</t>
+  </si>
+  <si>
+    <t>反计</t>
+  </si>
+  <si>
+    <t>若识破部队计略，就可对其施展同样的计略</t>
+  </si>
+  <si>
+    <t>奇谋</t>
+  </si>
+  <si>
+    <t>妖术</t>
+  </si>
+  <si>
+    <t>可施展部队计略的「妖术」</t>
+  </si>
+  <si>
+    <t>鬼门</t>
+  </si>
+  <si>
+    <t>可施展部队计略的「妖术、落雷」</t>
+  </si>
+  <si>
+    <t>可防止遭受部队计略「伪报」</t>
+  </si>
+  <si>
+    <t>补助</t>
+  </si>
+  <si>
+    <t>沉着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可防止遭受部队计略「扰乱」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可防止遭受部队计略的「伪报、扰乱」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奏乐</t>
+  </si>
+  <si>
+    <t>每回合回复自军部队的气力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>诗想</t>
+  </si>
+  <si>
+    <t>筑城</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>军事设施建设的耐久上升量增为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屯田</t>
+  </si>
+  <si>
+    <t>所属于关所、港口时，士兵不会消费兵粮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名声</t>
+  </si>
+  <si>
+    <t>增加征兵时的士兵数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能吏</t>
+  </si>
+  <si>
+    <t>增加生产枪、戟、弩之兵装时的产量</t>
+  </si>
+  <si>
+    <t>繁殖</t>
+  </si>
+  <si>
+    <t>增加生产军马之兵装时的产量</t>
+  </si>
+  <si>
+    <t>生产兵器之兵装时所需的生产期间减半</t>
+  </si>
+  <si>
+    <t>造船</t>
+  </si>
+  <si>
+    <t>生产舰船之兵装时所需的生产期间减半</t>
+  </si>
+  <si>
+    <t>指导</t>
+  </si>
+  <si>
+    <t>研究技巧时的费用减半</t>
+  </si>
+  <si>
+    <t>眼力</t>
+  </si>
+  <si>
+    <t>若有未发现的在野人士时执行人材探索的话，必定会发现</t>
+  </si>
+  <si>
+    <t>论客</t>
+  </si>
+  <si>
+    <t>于同盟、停战协定、交换俘虏时容易进入舌战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>富豪</t>
+  </si>
+  <si>
+    <t>每个月的所属都市的资金收入增为1.5倍</t>
+  </si>
+  <si>
+    <t>收入</t>
+  </si>
+  <si>
+    <t>米道</t>
+  </si>
+  <si>
+    <t>每季的所属都市的兵粮收入增加为1.5倍</t>
+  </si>
+  <si>
+    <t>征税</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合所属都市都会有资金收入（一次收入将减半）</t>
+  </si>
+  <si>
+    <t>征收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个月所属都市都会有兵粮的收入（一次的收入将减半）</t>
+  </si>
+  <si>
+    <t>亲乌</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「乌丸」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灾害</t>
+  </si>
+  <si>
+    <t>亲羌</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「羌族」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲越</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「山越」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲蛮</t>
+  </si>
+  <si>
+    <t>所属都市的领内不会出现异族「南蛮」的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>威压</t>
+  </si>
+  <si>
+    <t>所属都市的领内不容易出现盗贼或异族的根据地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仁政</t>
+  </si>
+  <si>
+    <t>所属相同的武将之每个月的忠诚不会下降</t>
+  </si>
+  <si>
+    <t>风水</t>
+  </si>
+  <si>
+    <t>所属都市不容易出现蝗灾、瘟疫</t>
+  </si>
+  <si>
+    <t>祈愿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属都市容易出现丰收</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内助</t>
+  </si>
+  <si>
+    <t>若结婚，双方的能力全部＋２</t>
+  </si>
+  <si>
+    <t>关系</t>
+  </si>
+  <si>
+    <t>u8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对部队施展部队计略成功率增为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必定可识破敌方部队所施展的部队计略,反击伤害增加为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actionEntities</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobResult", value:150, jobIds:[6]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobResult", value:200, jobIds:[8]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobResult", value:200, jobIds:[12]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[10]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[11]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加了反击伤害倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aobj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5],condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, isNormal:2, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:0, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2,3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>枪神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[11,12,13,14], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:1},{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[1,2,3,4,5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopIgnoreZOC", value:0}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[6]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[7]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[27], result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TerrainCheck",checkTarget:"self",terrainType:6} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillTargetCellCheck", targetType:"buildingBase", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopRecure",percent:10}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}, {class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateAttackBack", value:200, isDefender:1},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[24], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[25], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[24,25], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[22], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[24], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[25], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[28], result:1}] }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetSkillCost", value:1, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeSkillSpellRange", value:2, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeSkillSpellRange", value:1,  kinds:[13,14]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddSkill", value:2,  kinds:[5]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>深谋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>规律</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>明镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白马</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>待伏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hasInit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeCaptiveFactor", value:100}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeEscapeFactor", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangePersonEscapeFactor", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>捕缚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-20}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:-1,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSetDamage", value:-1,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddSkillAttackRange", "atkType":5,"addRange":1,condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerTroopTurnStart"}], actionList:[{class:"TroopChangeMorale",value:5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任何回复气力效果增为２倍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerTroopOnMoralChange"}], actionList:[{class:"TroopModifyMorale",value:20000}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>突袭</t>
-  </si>
-  <si>
-    <t>于陆上攻击时，不会受到损伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强袭</t>
-  </si>
-  <si>
-    <t>于水上攻击时，不会受到损伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乱战</t>
-  </si>
-  <si>
-    <t>于森林中攻击时施展会心一击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伏兵成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>计略</t>
-  </si>
-  <si>
-    <t>攻城</t>
-  </si>
-  <si>
-    <t>攻击据点、设施、建筑物时施展会心一击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掎角</t>
-  </si>
-  <si>
-    <t>施展齐攻时，让对方陷入混乱</t>
-  </si>
-  <si>
-    <t>击破敌方部队时，必定可捕捉无特技「强运」或名马的敌将</t>
-  </si>
-  <si>
-    <t>精妙</t>
-  </si>
-  <si>
-    <t>击破敌方部队时所获得的技巧点数增为２倍</t>
-  </si>
-  <si>
-    <t>掠夺</t>
-  </si>
-  <si>
-    <t>击破敌方部队时，有机会夺取敌将的道具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻心</t>
-  </si>
-  <si>
-    <t>攻击时可将敌方部队的一部分士兵吸收到自军部队中</t>
-  </si>
-  <si>
-    <t>驱逐</t>
-  </si>
-  <si>
-    <t>施展一般攻击时会心一击</t>
-  </si>
-  <si>
-    <t>射程</t>
-  </si>
-  <si>
-    <t>使井阑、投石的射程增加１区格</t>
-  </si>
-  <si>
-    <t>未研究技巧「骑射」时也可施展骑射；骑射可施展会心一击</t>
-  </si>
-  <si>
-    <t>辅佐</t>
-  </si>
-  <si>
-    <t>即使没建立人际关系（厌恶除外）也可获得支援攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不屈</t>
-  </si>
-  <si>
-    <t>若在部队的士兵不多时被攻击，不会受到损伤</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>金刚</t>
-  </si>
-  <si>
-    <t>在敌方攻击力微弱时被攻击的话，不会受到损伤</t>
-  </si>
-  <si>
-    <t>铁壁</t>
-  </si>
-  <si>
-    <t>就算被一齐攻击，也会视之为一般攻击</t>
-  </si>
-  <si>
-    <t>怒发</t>
-  </si>
-  <si>
-    <t>遭受敌方部队的战法攻击时，气力就会回复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>藤甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerTroopDestroyTroop"}], actionList:[{class:"TroopChangeMorale",value:10}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateAttackBack", value:0, checkLand:1, isDefender:0, condition:{class: "ProbabilityCheck",probability: 10000}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopSkillCalculateAttackBack", value:0, checkLand:2, isDefender:0, condition:{class: "ProbabilityCheck",probability: 10000}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>火以外的攻击损伤减半，但火攻的损伤将增为２倍</t>
-  </si>
-  <si>
-    <t>强运</t>
-  </si>
-  <si>
-    <t>不会战死、被俘、负伤</t>
-  </si>
-  <si>
-    <t>血路</t>
-  </si>
-  <si>
-    <t>就算部队溃灭，同部队的武将也不会被俘虏</t>
-  </si>
-  <si>
-    <t>枪将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展枪兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>戟将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展戟兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>弓将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展弩兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>骑将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展骑兵战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>水将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展水军战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>勇将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展全战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>神将</t>
-  </si>
-  <si>
-    <t>对武力比自己低的敌方部队施展一般攻击及战法成功时会心一击</t>
-  </si>
-  <si>
-    <t>斗神</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪兵战法与戟兵战法施展成功时会心一击</t>
-  </si>
-  <si>
-    <t>枪兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>戟神</t>
-  </si>
-  <si>
-    <t>戟兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>弓神</t>
-  </si>
-  <si>
-    <t>弩兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>骑神</t>
-  </si>
-  <si>
-    <t>骑兵战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>工神</t>
-  </si>
-  <si>
-    <t>兵器战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>水神</t>
-  </si>
-  <si>
-    <t>水军战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>霸王</t>
-  </si>
-  <si>
-    <t>全战法成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>疾驰</t>
-  </si>
-  <si>
-    <t>对攻击力比自部队低的敌方部队施展骑兵战法成功时，必使其陷入混乱</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>可于森林使用弩兵战法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>猛者</t>
-  </si>
-  <si>
-    <t>以战法让敌方部队移动区格时，可让敌将负伤</t>
-  </si>
-  <si>
-    <t>护卫</t>
-  </si>
-  <si>
-    <t>同部队的武将不会战死、负伤</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「火计」时必定会成功</t>
-  </si>
-  <si>
-    <t>言毒</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「伪报」时，必定会成功</t>
-  </si>
-  <si>
-    <t>机智</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「扰乱」时，必定会成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>诡计</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略「内讧」时，必定会成功</t>
-  </si>
-  <si>
-    <t>虚实</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展全部队计略时，必定会成功</t>
-  </si>
-  <si>
-    <t>妙计</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展部队计略成功时会心一击</t>
-  </si>
-  <si>
-    <t>秘计</t>
-  </si>
-  <si>
-    <t>对智力比自己高的敌方部队施展部队计略成功时会心一击</t>
-  </si>
-  <si>
-    <t>看破</t>
-  </si>
-  <si>
-    <t>必定可识破智力比自己低的敌方部队所施展部队计略</t>
-  </si>
-  <si>
-    <t>洞察</t>
-  </si>
-  <si>
-    <t>火神</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展火计时必会成功；于全火攻有所优势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神算</t>
-  </si>
-  <si>
-    <t>对智力比自己低的敌方部队施展计略必会成功；于全计略有所优势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>百出</t>
-  </si>
-  <si>
-    <t>部队计略的消费气力减少</t>
-  </si>
-  <si>
-    <t>鬼谋</t>
-  </si>
-  <si>
-    <t>增广２区格可施展部队计略的范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>连环</t>
-  </si>
-  <si>
-    <t>部队计略成功时，与对象部队邻接的部队也会遭受计略波及</t>
-  </si>
-  <si>
-    <t>部队计略成功时施展会心一击</t>
-  </si>
-  <si>
-    <t>反计</t>
-  </si>
-  <si>
-    <t>若识破部队计略，就可对其施展同样的计略</t>
-  </si>
-  <si>
-    <t>奇谋</t>
-  </si>
-  <si>
-    <t>妖术</t>
-  </si>
-  <si>
-    <t>可施展部队计略的「妖术」</t>
-  </si>
-  <si>
-    <t>鬼门</t>
-  </si>
-  <si>
-    <t>可施展部队计略的「妖术、落雷」</t>
-  </si>
-  <si>
-    <t>可防止遭受部队计略「伪报」</t>
-  </si>
-  <si>
-    <t>补助</t>
-  </si>
-  <si>
-    <t>沉着</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可防止遭受部队计略「扰乱」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可防止遭受部队计略的「伪报、扰乱」</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奏乐</t>
-  </si>
-  <si>
-    <t>每回合回复自军部队的气力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>诗想</t>
-  </si>
-  <si>
-    <t>筑城</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>军事设施建设的耐久上升量增为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屯田</t>
-  </si>
-  <si>
-    <t>所属于关所、港口时，士兵不会消费兵粮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名声</t>
-  </si>
-  <si>
-    <t>增加征兵时的士兵数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能吏</t>
-  </si>
-  <si>
-    <t>增加生产枪、戟、弩之兵装时的产量</t>
-  </si>
-  <si>
-    <t>繁殖</t>
-  </si>
-  <si>
-    <t>增加生产军马之兵装时的产量</t>
-  </si>
-  <si>
-    <t>生产兵器之兵装时所需的生产期间减半</t>
-  </si>
-  <si>
-    <t>造船</t>
-  </si>
-  <si>
-    <t>生产舰船之兵装时所需的生产期间减半</t>
-  </si>
-  <si>
-    <t>指导</t>
-  </si>
-  <si>
-    <t>研究技巧时的费用减半</t>
-  </si>
-  <si>
-    <t>眼力</t>
-  </si>
-  <si>
-    <t>若有未发现的在野人士时执行人材探索的话，必定会发现</t>
-  </si>
-  <si>
-    <t>论客</t>
-  </si>
-  <si>
-    <t>于同盟、停战协定、交换俘虏时容易进入舌战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>富豪</t>
-  </si>
-  <si>
-    <t>每个月的所属都市的资金收入增为1.5倍</t>
-  </si>
-  <si>
-    <t>收入</t>
-  </si>
-  <si>
-    <t>米道</t>
-  </si>
-  <si>
-    <t>每季的所属都市的兵粮收入增加为1.5倍</t>
-  </si>
-  <si>
-    <t>征税</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每回合所属都市都会有资金收入（一次收入将减半）</t>
-  </si>
-  <si>
-    <t>征收</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每个月所属都市都会有兵粮的收入（一次的收入将减半）</t>
-  </si>
-  <si>
-    <t>亲乌</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「乌丸」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灾害</t>
-  </si>
-  <si>
-    <t>亲羌</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「羌族」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亲越</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「山越」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亲蛮</t>
-  </si>
-  <si>
-    <t>所属都市的领内不会出现异族「南蛮」的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>威压</t>
-  </si>
-  <si>
-    <t>所属都市的领内不容易出现盗贼或异族的根据地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>仁政</t>
-  </si>
-  <si>
-    <t>所属相同的武将之每个月的忠诚不会下降</t>
-  </si>
-  <si>
-    <t>风水</t>
-  </si>
-  <si>
-    <t>所属都市不容易出现蝗灾、瘟疫</t>
-  </si>
-  <si>
-    <t>祈愿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属都市容易出现丰收</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>内助</t>
-  </si>
-  <si>
-    <t>若结婚，双方的能力全部＋２</t>
-  </si>
-  <si>
-    <t>关系</t>
-  </si>
-  <si>
-    <t>u8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对部队施展部队计略成功率增为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>必定可识破敌方部队所施展的部队计略,反击伤害增加为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>actionEntities</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobResult", value:150, jobIds:[6]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobResult", value:200, jobIds:[8]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobResult", value:200, jobIds:[12]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[10]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"CityImproveJobCounterResult", value:50, jobIds:[11]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>增加了反击伤害倍率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aobj</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5],condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, isNormal:2, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:0, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2,3], condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>枪神</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[2], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[3], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[4], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[5], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[11,12,13,14], condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, kinds:[8,9,10], checkLand:2, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopIgnoreZOC", value:1},{class:"TroopSkillCalculateCritical", value:100,condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"strength",result:1},{class:"SkillIsNormalSkill", result:0},{class:"SkillIsStrategySkill", result:0} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopIgnoreZOC", value:1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[5]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[1,2,3,4,5]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopIgnoreZOC", value:0}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[6]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddMoveAbility", value:8,  kinds:[7]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[27], result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TerrainCheck",checkTarget:"self",terrainType:6} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillTargetCellCheck", targetType:"buildingBase", result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, isNormal:1}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-5}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopRecure",percent:10}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}, {class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:-1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateAttackBack", value:200, isDefender:1},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"SkillIsStrategySkill", result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[24], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[25], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true",condition:{class:"andList",list:[{class:"SkillIdInList", ids:[24,25], result:1},{class:"SkillIsStrategySkill", result:1} ] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[22], result:1}] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[24], result:1}] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[25], result:1}] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"intelligence",result:1},{class:"SkillIdInList", ids:[28], result:1}] }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSetSkillCost", value:1, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeSkillSpellRange", value:2, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeSkillSpellRange", value:1,  kinds:[13,14]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddSkill", value:2,  kinds:[5]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>深谋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>规律</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>明镜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>白马</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>待伏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hasInit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeCaptiveFactor", value:100}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangeEscapeFactor", value:200}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopChangePersonEscapeFactor", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction",triggerList:[{class:"TriggerWhenSkillActionEnd"}],actionList:[{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[1,2], weight:[70,30],
+condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:0}] }
+},{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[2,3], weight:[70,30],
+condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:1}] }
+}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[
         {
-          "class": "TroopChangeSkillAttackRange",
-          "atkType": 5,
-          "atkRange": 1,
-          "condition": {
-            "class": "SkillIdInList",
-            "ids": [
+          class: "TroopChangeSkillAttackRange",
+          atkType: 5,
+          atkRange: 1,
+          condition: {
+            class: "SkillIdInList",
+            ids: [
               22,
               23,
               24,
@@ -999,54 +1049,30 @@
               27,
               28
             ],
-            "result": 1
+            result: 1
           }
         }
       ]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>捕缚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,value:-20}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillActionEnd"}],"actionList":[{"class": "TroopComboAttack","count": 1,"condition": {"class": "andList","list": [{"class": "SkillIsNormalSkill","result": 1}]},"comboCondition": {"class": "andList","list": [{"class": "ProbabilityCheck","probability": 5000}]}}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"class":"TroopTriggerAction","triggerList":[{"class":"TriggerWhenSkillActionEnd"}],"actionList":[{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[1,2], weight:[70,30],
-condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:0}] }
-},{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[2,3], weight:[70,30],
-condition:{class:"andList",list:[{class:"TroopAttributeCompare",attType:"attack",result:1},{class:"SkillIdInList", ids:[12,13,14], result:1} ,{class:"SkillIsCritical",result:1}] }
-}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSetDamage", value:-1,  isDefender:1, belowDamage:500, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}]  }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopSetDamage", value:-1,  isDefender:1, condition:{class:"andList", list:[{class:"SkillIsNormalSkill",result:1},{class:"ProbabilityCheck",probability:5000}, {class:"TroopAttributeCheck",attributeType:"troops",value:3000,operator:"lte"}]  }}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopAddSkillAttackRange", "atkType":5,"addRange":1,condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateCritical", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:100, condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopSkillCalculateSuccess", value:-100, selfIsTarget:"true", condition:{class:"SkillIdInList", ids:[22], result:1}},{class:"TroopIgnoreFire", value:1},{class:"TroopSetFireDamage", value:20000}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerTroopTurnStart"}], actionList:[{class:"TroopChangeMorale",value:5}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>任何回复气力效果增为２倍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerTroopOnMoralChange"}], actionList:[{class:"TroopModifyMorale",value:20000}]}]</t>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopChangeMorale",targetType:1,isDefender:true, value:5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>于森林使用弩兵战法时伤害增加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction",triggerList:[{class:"TriggerWhenSkillActionEnd"}],actionList:[{class: "TroopComboAttack",count: 1,condition: {class:"andList",list: [{class: "SkillIsNormalSkill",result: 1}]},comboCondition: {class: "andList",list: [{class: "ProbabilityCheck",probability: 5000}]}}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:50, isDefender:1},{class:"TroopModifyFireDamage",value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:150, isDefender:0,condition:{class:"TerrainCheck",terrainType:6}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1609,22 +1635,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.5" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
     <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1639,7 +1665,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1652,7 +1678,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1666,7 +1692,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1676,10 +1702,10 @@
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="16" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1696,19 +1722,19 @@
         <v>4</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1732,10 +1758,10 @@
         <v>16</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1759,10 +1785,10 @@
         <v>16</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1786,10 +1812,10 @@
         <v>16</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1813,10 +1839,10 @@
         <v>16</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1840,10 +1866,10 @@
         <v>16</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1867,10 +1893,10 @@
         <v>16</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1892,7 +1918,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1915,10 +1941,10 @@
         <v>16</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1940,7 +1966,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1963,10 +1989,10 @@
         <v>35</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -1989,10 +2015,10 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2012,8 +2038,11 @@
       <c r="H16" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I16" s="19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2036,18 +2065,18 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <v>14</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>42</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11">
@@ -2059,16 +2088,19 @@
       <c r="H18" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="I18" s="19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <v>15</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="11">
@@ -2080,16 +2112,19 @@
       <c r="H19" s="11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I19" s="19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="28">
         <v>16</v>
       </c>
       <c r="C20" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="28" t="s">
         <v>46</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>47</v>
       </c>
       <c r="E20" s="28">
         <v>1</v>
@@ -2104,18 +2139,18 @@
         <v>35</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="28">
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E21" s="28">
         <v>1</v>
@@ -2127,21 +2162,21 @@
         <v>4</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="28">
         <v>18</v>
       </c>
       <c r="C22" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>50</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>51</v>
       </c>
       <c r="E22" s="28">
         <v>1</v>
@@ -2156,18 +2191,18 @@
         <v>35</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="11">
         <v>19</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="11">
@@ -2180,15 +2215,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="28">
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E24" s="28"/>
       <c r="F24" s="28">
@@ -2201,18 +2236,18 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="11">
         <v>21</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>56</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="11">
@@ -2225,15 +2260,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="11">
         <v>22</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>58</v>
       </c>
       <c r="E26" s="11"/>
       <c r="F26" s="11">
@@ -2246,15 +2281,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="28">
         <v>23</v>
       </c>
       <c r="C27" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="28" t="s">
         <v>59</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>60</v>
       </c>
       <c r="E27" s="28">
         <v>1</v>
@@ -2269,18 +2304,18 @@
         <v>35</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="28">
         <v>24</v>
       </c>
       <c r="C28" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="28" t="s">
         <v>61</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>62</v>
       </c>
       <c r="E28" s="28">
         <v>1</v>
@@ -2295,18 +2330,18 @@
         <v>35</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="28">
         <v>25</v>
       </c>
       <c r="C29" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="28" t="s">
         <v>63</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>64</v>
       </c>
       <c r="E29" s="28">
         <v>1</v>
@@ -2321,18 +2356,18 @@
         <v>35</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="28">
         <v>26</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" s="28">
         <v>1</v>
@@ -2347,18 +2382,18 @@
         <v>35</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="11">
         <v>27</v>
       </c>
       <c r="C31" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="11">
@@ -2371,15 +2406,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="28">
         <v>28</v>
       </c>
       <c r="C32" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="28" t="s">
         <v>68</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>69</v>
       </c>
       <c r="E32" s="28"/>
       <c r="F32" s="28">
@@ -2389,21 +2424,21 @@
         <v>3</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28">
         <v>29</v>
       </c>
       <c r="C33" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="E33" s="28"/>
       <c r="F33" s="28">
@@ -2413,21 +2448,21 @@
         <v>3</v>
       </c>
       <c r="H33" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="11">
         <v>30</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>74</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="11">
@@ -2437,18 +2472,18 @@
         <v>3</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="11">
         <v>31</v>
       </c>
       <c r="C35" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="11">
@@ -2458,18 +2493,21 @@
         <v>3</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="11">
         <v>32</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>78</v>
+        <v>288</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="11">
@@ -2479,18 +2517,21 @@
         <v>3</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="28">
         <v>33</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E37" s="28"/>
       <c r="F37" s="28">
@@ -2500,21 +2541,21 @@
         <v>3</v>
       </c>
       <c r="H37" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="28">
         <v>34</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E38" s="28"/>
       <c r="F38" s="28">
@@ -2524,21 +2565,21 @@
         <v>3</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="14">
         <v>35</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E39" s="14">
         <v>1</v>
@@ -2553,18 +2594,18 @@
         <v>35</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="14">
         <v>36</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E40" s="14">
         <v>1</v>
@@ -2579,18 +2620,18 @@
         <v>35</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="14">
         <v>37</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E41" s="14">
         <v>1</v>
@@ -2605,18 +2646,18 @@
         <v>35</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="14">
         <v>38</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E42" s="14">
         <v>1</v>
@@ -2631,18 +2672,18 @@
         <v>35</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="14">
         <v>39</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E43" s="14">
         <v>1</v>
@@ -2657,18 +2698,18 @@
         <v>35</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="14">
         <v>40</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E44" s="14">
         <v>1</v>
@@ -2683,18 +2724,18 @@
         <v>35</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="14">
         <v>41</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E45" s="14">
         <v>1</v>
@@ -2709,18 +2750,18 @@
         <v>35</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="14">
         <v>42</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E46" s="14">
         <v>1</v>
@@ -2735,18 +2776,18 @@
         <v>35</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="14">
         <v>43</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E47" s="14">
         <v>1</v>
@@ -2761,18 +2802,18 @@
         <v>35</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="14">
         <v>44</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E48" s="14">
         <v>1</v>
@@ -2787,18 +2828,18 @@
         <v>35</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="14">
         <v>45</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E49" s="14">
         <v>1</v>
@@ -2813,18 +2854,18 @@
         <v>35</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="14">
         <v>46</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E50" s="14">
         <v>1</v>
@@ -2839,18 +2880,18 @@
         <v>35</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="14">
         <v>47</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E51" s="14">
         <v>1</v>
@@ -2865,18 +2906,18 @@
         <v>35</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="14">
         <v>48</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E52" s="14">
         <v>1</v>
@@ -2891,18 +2932,18 @@
         <v>35</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="14">
         <v>49</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E53" s="14">
         <v>1</v>
@@ -2917,18 +2958,18 @@
         <v>35</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="28">
         <v>50</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E54" s="14">
         <v>1</v>
@@ -2943,18 +2984,18 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="9">
         <v>51</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>115</v>
+        <v>292</v>
       </c>
       <c r="E55" s="9"/>
       <c r="F55" s="9">
@@ -2966,17 +3007,19 @@
       <c r="H55" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I55" s="20"/>
-    </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="I55" s="19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9">
         <v>52</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="9">
@@ -2990,15 +3033,15 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="11">
         <v>53</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="11">
@@ -3008,10 +3051,10 @@
         <v>3</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3019,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E58" s="28">
         <v>1</v>
@@ -3031,21 +3074,21 @@
         <v>4</v>
       </c>
       <c r="H58" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28">
         <v>55</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E59" s="28">
         <v>1</v>
@@ -3057,21 +3100,21 @@
         <v>4</v>
       </c>
       <c r="H59" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28">
         <v>56</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E60" s="28">
         <v>1</v>
@@ -3083,21 +3126,21 @@
         <v>4</v>
       </c>
       <c r="H60" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="28">
         <v>57</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E61" s="28">
         <v>1</v>
@@ -3109,21 +3152,21 @@
         <v>4</v>
       </c>
       <c r="H61" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="28">
         <v>58</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E62" s="28">
         <v>1</v>
@@ -3135,21 +3178,21 @@
         <v>4</v>
       </c>
       <c r="H62" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="28">
         <v>59</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E63" s="28">
         <v>1</v>
@@ -3161,21 +3204,21 @@
         <v>4</v>
       </c>
       <c r="H63" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="28">
         <v>60</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E64" s="28">
         <v>1</v>
@@ -3187,21 +3230,21 @@
         <v>4</v>
       </c>
       <c r="H64" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="28">
         <v>61</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E65" s="28">
         <v>1</v>
@@ -3213,21 +3256,21 @@
         <v>4</v>
       </c>
       <c r="H65" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="14">
         <v>62</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E66" s="28">
         <v>1</v>
@@ -3239,24 +3282,24 @@
         <v>4</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="28">
         <v>63</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E67" s="28">
         <v>1</v>
@@ -3268,21 +3311,21 @@
         <v>4</v>
       </c>
       <c r="H67" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="28">
         <v>64</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E68" s="28">
         <v>1</v>
@@ -3294,21 +3337,21 @@
         <v>4</v>
       </c>
       <c r="H68" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="28">
         <v>65</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E69" s="28">
         <v>1</v>
@@ -3320,21 +3363,21 @@
         <v>4</v>
       </c>
       <c r="H69" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="28">
         <v>66</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E70" s="28">
         <v>1</v>
@@ -3346,21 +3389,21 @@
         <v>4</v>
       </c>
       <c r="H70" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
       <c r="B71" s="28">
         <v>67</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E71" s="28"/>
       <c r="F71" s="28">
@@ -3370,21 +3413,21 @@
         <v>4</v>
       </c>
       <c r="H71" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="28">
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E72" s="28">
         <v>1</v>
@@ -3396,21 +3439,21 @@
         <v>4</v>
       </c>
       <c r="H72" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="11">
         <v>69</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E73" s="11"/>
       <c r="F73" s="11">
@@ -3420,18 +3463,18 @@
         <v>4</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="11">
         <v>70</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E74" s="11"/>
       <c r="F74" s="11">
@@ -3441,18 +3484,18 @@
         <v>4</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="11">
         <v>71</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E75" s="11"/>
       <c r="F75" s="11">
@@ -3462,18 +3505,18 @@
         <v>4</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="11">
         <v>72</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="11">
@@ -3483,18 +3526,18 @@
         <v>4</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="28">
         <v>73</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E77" s="28">
         <v>1</v>
@@ -3506,21 +3549,21 @@
         <v>5</v>
       </c>
       <c r="H77" s="28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="28">
         <v>74</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E78" s="28">
         <v>1</v>
@@ -3532,21 +3575,21 @@
         <v>5</v>
       </c>
       <c r="H78" s="28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="28">
         <v>75</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E79" s="28">
         <v>1</v>
@@ -3558,21 +3601,21 @@
         <v>5</v>
       </c>
       <c r="H79" s="28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="14">
         <v>76</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E80" s="14"/>
       <c r="F80" s="14">
@@ -3582,21 +3625,21 @@
         <v>5</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="14">
         <v>77</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="E81" s="14"/>
       <c r="F81" s="14">
@@ -3606,21 +3649,21 @@
         <v>5</v>
       </c>
       <c r="H81" s="14" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="9">
         <v>78</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="9">
@@ -3630,19 +3673,19 @@
         <v>5</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="9">
         <v>79</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E83" s="9"/>
       <c r="F83" s="9">
@@ -3652,19 +3695,19 @@
         <v>5</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="14">
         <v>80</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E84" s="14">
         <v>1</v>
@@ -3673,24 +3716,24 @@
         <v>2</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H84" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="14">
         <v>81</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E85" s="14">
         <v>1</v>
@@ -3699,24 +3742,24 @@
         <v>2</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H85" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="14">
         <v>82</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E86" s="14">
         <v>1</v>
@@ -3725,16 +3768,16 @@
         <v>2</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H86" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3742,7 +3785,7 @@
         <v>8</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E87" s="14">
         <v>1</v>
@@ -3751,24 +3794,24 @@
         <v>2</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H87" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="14">
         <v>84</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E88" s="14">
         <v>1</v>
@@ -3777,46 +3820,46 @@
         <v>2</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H88" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I88" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="9">
         <v>85</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E89" s="9"/>
       <c r="F89" s="9">
         <v>2</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>10</v>
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="9">
         <v>86</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E90" s="9"/>
       <c r="F90" s="9">
@@ -3830,15 +3873,15 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="9">
         <v>87</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E91" s="9"/>
       <c r="F91" s="9">
@@ -3852,15 +3895,15 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="9">
         <v>88</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E92" s="9"/>
       <c r="F92" s="9">
@@ -3870,19 +3913,19 @@
         <v>7</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I92" s="17"/>
     </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="9">
         <v>89</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9">
@@ -3892,19 +3935,19 @@
         <v>7</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I93" s="20"/>
     </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="9">
         <v>90</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9">
@@ -3914,19 +3957,19 @@
         <v>7</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I94" s="20"/>
     </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="9">
         <v>91</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9">
@@ -3936,19 +3979,19 @@
         <v>7</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I95" s="20"/>
     </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="9">
         <v>92</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9">
@@ -3958,19 +4001,19 @@
         <v>8</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="9">
         <v>93</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9">
@@ -3980,19 +4023,19 @@
         <v>8</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="9">
         <v>94</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9">
@@ -4002,19 +4045,19 @@
         <v>8</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B99" s="9">
         <v>95</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E99" s="9"/>
       <c r="F99" s="9">
@@ -4024,19 +4067,19 @@
         <v>8</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B100" s="9">
         <v>96</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E100" s="9"/>
       <c r="F100" s="9">
@@ -4046,19 +4089,19 @@
         <v>8</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B101" s="9">
         <v>97</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E101" s="9"/>
       <c r="F101" s="9">
@@ -4068,19 +4111,19 @@
         <v>8</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B102" s="9">
         <v>98</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E102" s="9"/>
       <c r="F102" s="9">
@@ -4090,19 +4133,19 @@
         <v>8</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="9">
         <v>99</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E103" s="9"/>
       <c r="F103" s="9">
@@ -4112,19 +4155,19 @@
         <v>8</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="9">
         <v>100</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E104" s="9"/>
       <c r="F104" s="9">
@@ -4134,7 +4177,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I104" s="20"/>
     </row>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFFEC01-3B49-4927-B5B8-3095CE4457ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF5C441-32E9-4C6B-94AC-C1CC1E2C5FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="304">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -954,10 +954,6 @@
   </si>
   <si>
     <t>待伏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hasInit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1075,12 +1071,48 @@
     <t>[{class:"TroopChangeDamage", value:150, isDefender:0,condition:{class:"TerrainCheck",terrainType:6}}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>only</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveFoodHarvest", value:150}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveGoldHarvest", value:150}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityGoldHarvestEveryTurn", value:150}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityFoodHarvestEveryMonth", value:150}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopImproveSkillSuccess", value:200, condition:{class:"SkillIsStrategySkill", result:1}}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction",triggerList:[{class:"TriggerWhenSkillActionEnd"}],actionList:[{class: "TroopSkillBack",condition: {class:"andList",list: [{class: "SkillIsStrategySkill",result: 1},{class: "ProbabilityCheck",probability: 5000}]}}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1146,6 +1178,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1229,7 +1268,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1322,6 +1361,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1635,22 +1680,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:J104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="70.453125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="254.6328125" style="17" customWidth="1"/>
-    <col min="10" max="10" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="254.625" style="17" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8"/>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -1665,7 +1710,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="16"/>
     </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1678,7 +1723,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="17"/>
     </row>
-    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="3" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1692,7 +1737,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1705,7 +1750,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -1719,7 +1764,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>4</v>
+        <v>296</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>207</v>
@@ -1734,7 +1779,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="25"/>
       <c r="B5" s="26">
         <v>1</v>
@@ -1745,8 +1790,8 @@
       <c r="D5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="26">
-        <v>1</v>
+      <c r="E5" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F5" s="26">
         <v>4</v>
@@ -1761,7 +1806,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" s="27"/>
       <c r="B6" s="28">
         <v>2</v>
@@ -1772,8 +1817,8 @@
       <c r="D6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="28">
-        <v>1</v>
+      <c r="E6" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F6" s="28">
         <v>3</v>
@@ -1788,7 +1833,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="29"/>
       <c r="B7" s="28">
         <v>3</v>
@@ -1799,8 +1844,8 @@
       <c r="D7" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="26">
-        <v>1</v>
+      <c r="E7" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F7" s="28">
         <v>3</v>
@@ -1815,7 +1860,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="29"/>
       <c r="B8" s="28">
         <v>4</v>
@@ -1826,8 +1871,8 @@
       <c r="D8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="28">
-        <v>1</v>
+      <c r="E8" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F8" s="28">
         <v>2</v>
@@ -1842,7 +1887,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" s="29"/>
       <c r="B9" s="28">
         <v>5</v>
@@ -1853,8 +1898,8 @@
       <c r="D9" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="26">
-        <v>1</v>
+      <c r="E9" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F9" s="28">
         <v>2</v>
@@ -1869,7 +1914,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="29"/>
       <c r="B10" s="28">
         <v>6</v>
@@ -1880,8 +1925,8 @@
       <c r="D10" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="28">
-        <v>1</v>
+      <c r="E10" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F10" s="28">
         <v>2</v>
@@ -1896,7 +1941,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="9">
         <v>7</v>
       </c>
@@ -1906,7 +1951,9 @@
       <c r="D11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F11" s="9">
         <v>2</v>
       </c>
@@ -1918,7 +1965,7 @@
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="28">
         <v>8</v>
       </c>
@@ -1928,8 +1975,8 @@
       <c r="D12" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="28">
-        <v>1</v>
+      <c r="E12" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F12" s="28">
         <v>2</v>
@@ -1944,7 +1991,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="9">
         <v>9</v>
       </c>
@@ -1954,7 +2001,9 @@
       <c r="D13" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="9"/>
+      <c r="E13" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F13" s="9">
         <v>2</v>
       </c>
@@ -1966,7 +2015,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="28">
         <v>10</v>
       </c>
@@ -1976,8 +2025,8 @@
       <c r="D14" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="28">
-        <v>1</v>
+      <c r="E14" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F14" s="28">
         <v>2</v>
@@ -1992,7 +2041,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B15" s="28">
         <v>11</v>
       </c>
@@ -2002,8 +2051,8 @@
       <c r="D15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="28">
-        <v>1</v>
+      <c r="E15" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F15" s="28">
         <v>3</v>
@@ -2015,10 +2064,10 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="11">
         <v>12</v>
       </c>
@@ -2028,7 +2077,9 @@
       <c r="D16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="11"/>
+      <c r="E16" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F16" s="11">
         <v>2</v>
       </c>
@@ -2039,10 +2090,10 @@
         <v>35</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B17" s="28">
         <v>13</v>
       </c>
@@ -2052,8 +2103,8 @@
       <c r="D17" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="28">
-        <v>1</v>
+      <c r="E17" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F17" s="28">
         <v>2</v>
@@ -2065,20 +2116,22 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="11">
         <v>14</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="11"/>
+      <c r="E18" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F18" s="11">
         <v>2</v>
       </c>
@@ -2089,10 +2142,10 @@
         <v>35</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="11">
         <v>15</v>
       </c>
@@ -2102,7 +2155,9 @@
       <c r="D19" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F19" s="11">
         <v>2</v>
       </c>
@@ -2113,10 +2168,10 @@
         <v>35</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B20" s="28">
         <v>16</v>
       </c>
@@ -2126,8 +2181,8 @@
       <c r="D20" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="28">
-        <v>1</v>
+      <c r="E20" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F20" s="28">
         <v>2</v>
@@ -2142,7 +2197,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B21" s="28">
         <v>17</v>
       </c>
@@ -2152,8 +2207,8 @@
       <c r="D21" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E21" s="28">
-        <v>1</v>
+      <c r="E21" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F21" s="28">
         <v>2</v>
@@ -2168,7 +2223,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B22" s="28">
         <v>18</v>
       </c>
@@ -2178,8 +2233,8 @@
       <c r="D22" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="28">
-        <v>1</v>
+      <c r="E22" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F22" s="28">
         <v>3</v>
@@ -2194,7 +2249,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2204,7 +2259,9 @@
       <c r="D23" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F23" s="11">
         <v>2</v>
       </c>
@@ -2215,17 +2272,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="28">
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D24" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="28"/>
+      <c r="E24" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F24" s="28">
         <v>2</v>
       </c>
@@ -2236,10 +2295,10 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B25" s="11">
         <v>21</v>
       </c>
@@ -2249,7 +2308,9 @@
       <c r="D25" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="11"/>
+      <c r="E25" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F25" s="11">
         <v>2</v>
       </c>
@@ -2260,7 +2321,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B26" s="11">
         <v>22</v>
       </c>
@@ -2270,7 +2331,9 @@
       <c r="D26" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="11"/>
+      <c r="E26" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F26" s="11">
         <v>2</v>
       </c>
@@ -2281,7 +2344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B27" s="28">
         <v>23</v>
       </c>
@@ -2291,8 +2354,8 @@
       <c r="D27" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="28">
-        <v>1</v>
+      <c r="E27" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F27" s="28">
         <v>2</v>
@@ -2307,7 +2370,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B28" s="28">
         <v>24</v>
       </c>
@@ -2317,8 +2380,8 @@
       <c r="D28" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="28">
-        <v>1</v>
+      <c r="E28" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F28" s="28">
         <v>3</v>
@@ -2333,7 +2396,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B29" s="28">
         <v>25</v>
       </c>
@@ -2343,8 +2406,8 @@
       <c r="D29" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="28">
-        <v>1</v>
+      <c r="E29" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F29" s="28">
         <v>2</v>
@@ -2359,7 +2422,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B30" s="28">
         <v>26</v>
       </c>
@@ -2369,8 +2432,8 @@
       <c r="D30" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="28">
-        <v>1</v>
+      <c r="E30" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F30" s="28">
         <v>2</v>
@@ -2385,7 +2448,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B31" s="11">
         <v>27</v>
       </c>
@@ -2395,7 +2458,9 @@
       <c r="D31" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F31" s="11">
         <v>2</v>
       </c>
@@ -2406,7 +2471,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B32" s="28">
         <v>28</v>
       </c>
@@ -2416,7 +2481,9 @@
       <c r="D32" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="28"/>
+      <c r="E32" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F32" s="28">
         <v>2</v>
       </c>
@@ -2427,10 +2494,10 @@
         <v>69</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B33" s="28">
         <v>29</v>
       </c>
@@ -2440,7 +2507,9 @@
       <c r="D33" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="28"/>
+      <c r="E33" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F33" s="28">
         <v>2</v>
       </c>
@@ -2451,10 +2520,10 @@
         <v>69</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B34" s="11">
         <v>30</v>
       </c>
@@ -2464,7 +2533,9 @@
       <c r="D34" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="11"/>
+      <c r="E34" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F34" s="11">
         <v>2</v>
       </c>
@@ -2475,7 +2546,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B35" s="11">
         <v>31</v>
       </c>
@@ -2485,7 +2556,9 @@
       <c r="D35" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="11"/>
+      <c r="E35" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F35" s="11">
         <v>2</v>
       </c>
@@ -2496,10 +2569,10 @@
         <v>69</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" s="11">
         <v>32</v>
       </c>
@@ -2507,9 +2580,11 @@
         <v>76</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="E36" s="11"/>
+        <v>287</v>
+      </c>
+      <c r="E36" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F36" s="11">
         <v>2</v>
       </c>
@@ -2520,10 +2595,10 @@
         <v>69</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B37" s="28">
         <v>33</v>
       </c>
@@ -2533,7 +2608,9 @@
       <c r="D37" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="28"/>
+      <c r="E37" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F37" s="28">
         <v>4</v>
       </c>
@@ -2544,10 +2621,10 @@
         <v>69</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B38" s="28">
         <v>34</v>
       </c>
@@ -2557,7 +2634,9 @@
       <c r="D38" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="E38" s="28"/>
+      <c r="E38" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F38" s="28">
         <v>2</v>
       </c>
@@ -2568,10 +2647,10 @@
         <v>69</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="14">
         <v>35</v>
       </c>
@@ -2581,8 +2660,8 @@
       <c r="D39" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E39" s="14">
-        <v>1</v>
+      <c r="E39" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F39" s="14">
         <v>2</v>
@@ -2597,7 +2676,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B40" s="14">
         <v>36</v>
       </c>
@@ -2607,8 +2686,8 @@
       <c r="D40" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E40" s="14">
-        <v>1</v>
+      <c r="E40" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F40" s="14">
         <v>2</v>
@@ -2623,7 +2702,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B41" s="14">
         <v>37</v>
       </c>
@@ -2633,8 +2712,8 @@
       <c r="D41" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="14">
-        <v>1</v>
+      <c r="E41" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F41" s="14">
         <v>2</v>
@@ -2649,7 +2728,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B42" s="14">
         <v>38</v>
       </c>
@@ -2659,8 +2738,8 @@
       <c r="D42" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E42" s="14">
-        <v>1</v>
+      <c r="E42" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F42" s="14">
         <v>2</v>
@@ -2675,7 +2754,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B43" s="14">
         <v>39</v>
       </c>
@@ -2685,8 +2764,8 @@
       <c r="D43" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E43" s="14">
-        <v>1</v>
+      <c r="E43" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F43" s="14">
         <v>2</v>
@@ -2701,7 +2780,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B44" s="14">
         <v>40</v>
       </c>
@@ -2711,8 +2790,8 @@
       <c r="D44" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="14">
-        <v>1</v>
+      <c r="E44" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F44" s="14">
         <v>3</v>
@@ -2727,7 +2806,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B45" s="14">
         <v>41</v>
       </c>
@@ -2737,8 +2816,8 @@
       <c r="D45" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E45" s="14">
-        <v>1</v>
+      <c r="E45" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F45" s="14">
         <v>4</v>
@@ -2753,7 +2832,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B46" s="14">
         <v>42</v>
       </c>
@@ -2763,8 +2842,8 @@
       <c r="D46" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E46" s="14">
-        <v>1</v>
+      <c r="E46" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F46" s="14">
         <v>3</v>
@@ -2779,7 +2858,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B47" s="14">
         <v>43</v>
       </c>
@@ -2789,8 +2868,8 @@
       <c r="D47" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="E47" s="14">
-        <v>1</v>
+      <c r="E47" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F47" s="14">
         <v>3</v>
@@ -2805,7 +2884,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B48" s="14">
         <v>44</v>
       </c>
@@ -2815,8 +2894,8 @@
       <c r="D48" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E48" s="14">
-        <v>1</v>
+      <c r="E48" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F48" s="14">
         <v>3</v>
@@ -2831,7 +2910,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B49" s="14">
         <v>45</v>
       </c>
@@ -2841,8 +2920,8 @@
       <c r="D49" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E49" s="14">
-        <v>1</v>
+      <c r="E49" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F49" s="14">
         <v>3</v>
@@ -2857,7 +2936,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B50" s="14">
         <v>46</v>
       </c>
@@ -2867,8 +2946,8 @@
       <c r="D50" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="14">
-        <v>1</v>
+      <c r="E50" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F50" s="14">
         <v>3</v>
@@ -2883,7 +2962,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B51" s="14">
         <v>47</v>
       </c>
@@ -2893,8 +2972,8 @@
       <c r="D51" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E51" s="14">
-        <v>1</v>
+      <c r="E51" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F51" s="14">
         <v>3</v>
@@ -2909,7 +2988,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B52" s="14">
         <v>48</v>
       </c>
@@ -2919,8 +2998,8 @@
       <c r="D52" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="14">
-        <v>1</v>
+      <c r="E52" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F52" s="14">
         <v>3</v>
@@ -2935,7 +3014,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B53" s="14">
         <v>49</v>
       </c>
@@ -2945,8 +3024,8 @@
       <c r="D53" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E53" s="14">
-        <v>1</v>
+      <c r="E53" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F53" s="14">
         <v>4</v>
@@ -2961,7 +3040,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="28">
         <v>50</v>
       </c>
@@ -2971,8 +3050,8 @@
       <c r="D54" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="E54" s="14">
-        <v>1</v>
+      <c r="E54" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F54" s="28">
         <v>3</v>
@@ -2984,10 +3063,10 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B55" s="9">
         <v>51</v>
       </c>
@@ -2995,9 +3074,11 @@
         <v>112</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="E55" s="9"/>
+        <v>291</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F55" s="9">
         <v>2</v>
       </c>
@@ -3008,10 +3089,10 @@
         <v>35</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B56" s="9">
         <v>52</v>
       </c>
@@ -3021,7 +3102,9 @@
       <c r="D56" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E56" s="9"/>
+      <c r="E56" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F56" s="9">
         <v>2</v>
       </c>
@@ -3033,7 +3116,7 @@
       </c>
       <c r="I56" s="20"/>
     </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B57" s="11">
         <v>53</v>
       </c>
@@ -3043,7 +3126,9 @@
       <c r="D57" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="E57" s="11"/>
+      <c r="E57" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F57" s="11">
         <v>2</v>
       </c>
@@ -3054,7 +3139,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B58" s="28">
         <v>54</v>
       </c>
@@ -3064,8 +3149,8 @@
       <c r="D58" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="E58" s="28">
-        <v>1</v>
+      <c r="E58" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F58" s="28">
         <v>3</v>
@@ -3080,7 +3165,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B59" s="28">
         <v>55</v>
       </c>
@@ -3090,8 +3175,8 @@
       <c r="D59" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="E59" s="28">
-        <v>1</v>
+      <c r="E59" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F59" s="28">
         <v>3</v>
@@ -3106,7 +3191,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B60" s="28">
         <v>56</v>
       </c>
@@ -3116,8 +3201,8 @@
       <c r="D60" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="E60" s="28">
-        <v>1</v>
+      <c r="E60" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F60" s="28">
         <v>3</v>
@@ -3132,7 +3217,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B61" s="28">
         <v>57</v>
       </c>
@@ -3142,8 +3227,8 @@
       <c r="D61" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="E61" s="28">
-        <v>1</v>
+      <c r="E61" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F61" s="28">
         <v>3</v>
@@ -3158,7 +3243,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B62" s="28">
         <v>58</v>
       </c>
@@ -3168,8 +3253,8 @@
       <c r="D62" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="E62" s="28">
-        <v>1</v>
+      <c r="E62" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F62" s="28">
         <v>4</v>
@@ -3184,7 +3269,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B63" s="28">
         <v>59</v>
       </c>
@@ -3194,8 +3279,8 @@
       <c r="D63" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E63" s="28">
-        <v>1</v>
+      <c r="E63" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F63" s="28">
         <v>2</v>
@@ -3210,7 +3295,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B64" s="28">
         <v>60</v>
       </c>
@@ -3220,8 +3305,8 @@
       <c r="D64" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="E64" s="28">
-        <v>1</v>
+      <c r="E64" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F64" s="28">
         <v>2</v>
@@ -3236,7 +3321,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B65" s="28">
         <v>61</v>
       </c>
@@ -3246,8 +3331,8 @@
       <c r="D65" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="E65" s="28">
-        <v>1</v>
+      <c r="E65" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F65" s="28">
         <v>3</v>
@@ -3262,7 +3347,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B66" s="14">
         <v>62</v>
       </c>
@@ -3272,8 +3357,8 @@
       <c r="D66" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="E66" s="28">
-        <v>1</v>
+      <c r="E66" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F66" s="14">
         <v>4</v>
@@ -3291,7 +3376,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="28">
         <v>63</v>
       </c>
@@ -3301,8 +3386,8 @@
       <c r="D67" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="E67" s="28">
-        <v>1</v>
+      <c r="E67" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F67" s="28">
         <v>4</v>
@@ -3314,10 +3399,10 @@
         <v>48</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B68" s="28">
         <v>64</v>
       </c>
@@ -3327,8 +3412,8 @@
       <c r="D68" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="E68" s="28">
-        <v>1</v>
+      <c r="E68" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F68" s="28">
         <v>4</v>
@@ -3343,7 +3428,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B69" s="28">
         <v>65</v>
       </c>
@@ -3353,8 +3438,8 @@
       <c r="D69" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="E69" s="28">
-        <v>1</v>
+      <c r="E69" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F69" s="28">
         <v>4</v>
@@ -3369,7 +3454,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B70" s="28">
         <v>66</v>
       </c>
@@ -3379,8 +3464,8 @@
       <c r="D70" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="E70" s="28">
-        <v>1</v>
+      <c r="E70" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F70" s="28">
         <v>3</v>
@@ -3395,7 +3480,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="71" spans="2:10" s="29" customFormat="1" ht="280" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
       <c r="B71" s="28">
         <v>67</v>
       </c>
@@ -3405,7 +3490,9 @@
       <c r="D71" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="E71" s="28"/>
+      <c r="E71" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F71" s="28">
         <v>3</v>
       </c>
@@ -3416,10 +3503,10 @@
         <v>48</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B72" s="28">
         <v>68</v>
       </c>
@@ -3429,8 +3516,8 @@
       <c r="D72" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="E72" s="28">
-        <v>1</v>
+      <c r="E72" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F72" s="28">
         <v>3</v>
@@ -3445,7 +3532,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B73" s="11">
         <v>69</v>
       </c>
@@ -3455,7 +3542,9 @@
       <c r="D73" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="E73" s="11"/>
+      <c r="E73" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F73" s="11">
         <v>3</v>
       </c>
@@ -3465,8 +3554,11 @@
       <c r="H73" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I73" s="24" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B74" s="11">
         <v>70</v>
       </c>
@@ -3476,7 +3568,9 @@
       <c r="D74" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="E74" s="11"/>
+      <c r="E74" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F74" s="11">
         <v>3</v>
       </c>
@@ -3486,8 +3580,11 @@
       <c r="H74" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I74" s="19" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B75" s="11">
         <v>71</v>
       </c>
@@ -3497,7 +3594,9 @@
       <c r="D75" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="E75" s="11"/>
+      <c r="E75" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F75" s="11">
         <v>3</v>
       </c>
@@ -3508,7 +3607,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B76" s="11">
         <v>72</v>
       </c>
@@ -3518,7 +3617,9 @@
       <c r="D76" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="E76" s="11"/>
+      <c r="E76" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F76" s="11">
         <v>4</v>
       </c>
@@ -3529,7 +3630,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B77" s="28">
         <v>73</v>
       </c>
@@ -3539,8 +3640,8 @@
       <c r="D77" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="E77" s="28">
-        <v>1</v>
+      <c r="E77" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F77" s="28">
         <v>2</v>
@@ -3555,7 +3656,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B78" s="28">
         <v>74</v>
       </c>
@@ -3565,8 +3666,8 @@
       <c r="D78" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="E78" s="28">
-        <v>1</v>
+      <c r="E78" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F78" s="28">
         <v>2</v>
@@ -3581,7 +3682,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B79" s="28">
         <v>75</v>
       </c>
@@ -3591,8 +3692,8 @@
       <c r="D79" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="E79" s="28">
-        <v>1</v>
+      <c r="E79" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F79" s="28">
         <v>3</v>
@@ -3607,7 +3708,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="80" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B80" s="14">
         <v>76</v>
       </c>
@@ -3617,7 +3718,9 @@
       <c r="D80" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="E80" s="14"/>
+      <c r="E80" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F80" s="14">
         <v>3</v>
       </c>
@@ -3628,10 +3731,10 @@
         <v>152</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B81" s="14">
         <v>77</v>
       </c>
@@ -3639,9 +3742,11 @@
         <v>158</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E81" s="14"/>
+        <v>281</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F81" s="14">
         <v>2</v>
       </c>
@@ -3652,10 +3757,10 @@
         <v>152</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B82" s="9">
         <v>78</v>
       </c>
@@ -3665,7 +3770,9 @@
       <c r="D82" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="E82" s="9"/>
+      <c r="E82" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F82" s="9">
         <v>2</v>
       </c>
@@ -3677,7 +3784,7 @@
       </c>
       <c r="I82" s="20"/>
     </row>
-    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
@@ -3687,19 +3794,21 @@
       <c r="D83" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E83" s="9"/>
+      <c r="E83" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F83" s="9">
         <v>2</v>
       </c>
-      <c r="G83" s="11">
-        <v>5</v>
+      <c r="G83" s="9">
+        <v>7</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="I83" s="20"/>
     </row>
-    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="14">
         <v>80</v>
       </c>
@@ -3709,8 +3818,8 @@
       <c r="D84" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E84" s="14">
-        <v>1</v>
+      <c r="E84" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F84" s="14">
         <v>2</v>
@@ -3725,7 +3834,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B85" s="14">
         <v>81</v>
       </c>
@@ -3735,8 +3844,8 @@
       <c r="D85" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E85" s="14">
-        <v>1</v>
+      <c r="E85" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F85" s="14">
         <v>2</v>
@@ -3751,7 +3860,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B86" s="14">
         <v>82</v>
       </c>
@@ -3761,8 +3870,8 @@
       <c r="D86" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="E86" s="14">
-        <v>1</v>
+      <c r="E86" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F86" s="14">
         <v>2</v>
@@ -3777,7 +3886,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B87" s="14">
         <v>83</v>
       </c>
@@ -3787,8 +3896,8 @@
       <c r="D87" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E87" s="14">
-        <v>1</v>
+      <c r="E87" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F87" s="14">
         <v>2</v>
@@ -3803,7 +3912,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B88" s="14">
         <v>84</v>
       </c>
@@ -3813,8 +3922,8 @@
       <c r="D88" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E88" s="14">
-        <v>1</v>
+      <c r="E88" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="F88" s="14">
         <v>2</v>
@@ -3829,7 +3938,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B89" s="9">
         <v>85</v>
       </c>
@@ -3839,7 +3948,9 @@
       <c r="D89" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E89" s="9"/>
+      <c r="E89" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F89" s="9">
         <v>2</v>
       </c>
@@ -3851,7 +3962,7 @@
       </c>
       <c r="I89" s="20"/>
     </row>
-    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
@@ -3861,7 +3972,9 @@
       <c r="D90" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E90" s="9"/>
+      <c r="E90" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F90" s="9">
         <v>2</v>
       </c>
@@ -3873,7 +3986,7 @@
       </c>
       <c r="I90" s="20"/>
     </row>
-    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
@@ -3883,7 +3996,9 @@
       <c r="D91" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="E91" s="9"/>
+      <c r="E91" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F91" s="9">
         <v>2</v>
       </c>
@@ -3895,51 +4010,59 @@
       </c>
       <c r="I91" s="20"/>
     </row>
-    <row r="92" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="9">
+    <row r="92" spans="2:9" s="33" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B92" s="32">
         <v>88</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D92" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9">
+      <c r="E92" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="F92" s="32">
         <v>3</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="32">
         <v>7</v>
       </c>
-      <c r="H92" s="9" t="s">
+      <c r="H92" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="I92" s="17"/>
-    </row>
-    <row r="93" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="9">
+      <c r="I92" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" s="33" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B93" s="32">
         <v>89</v>
       </c>
-      <c r="C93" s="9" t="s">
+      <c r="C93" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D93" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9">
+      <c r="E93" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="F93" s="32">
         <v>3</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93" s="32">
         <v>7</v>
       </c>
-      <c r="H93" s="9" t="s">
+      <c r="H93" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="I93" s="20"/>
-    </row>
-    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I93" s="19" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B94" s="9">
         <v>90</v>
       </c>
@@ -3949,7 +4072,9 @@
       <c r="D94" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E94" s="9"/>
+      <c r="E94" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F94" s="9">
         <v>3</v>
       </c>
@@ -3959,9 +4084,11 @@
       <c r="H94" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="I94" s="20"/>
-    </row>
-    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I94" s="19" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B95" s="9">
         <v>91</v>
       </c>
@@ -3971,7 +4098,9 @@
       <c r="D95" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="E95" s="9"/>
+      <c r="E95" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F95" s="9">
         <v>3</v>
       </c>
@@ -3981,9 +4110,11 @@
       <c r="H95" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="I95" s="20"/>
-    </row>
-    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I95" s="19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B96" s="9">
         <v>92</v>
       </c>
@@ -3993,7 +4124,9 @@
       <c r="D96" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="E96" s="9"/>
+      <c r="E96" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F96" s="9">
         <v>2</v>
       </c>
@@ -4005,7 +4138,7 @@
       </c>
       <c r="I96" s="20"/>
     </row>
-    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B97" s="9">
         <v>93</v>
       </c>
@@ -4015,7 +4148,9 @@
       <c r="D97" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="E97" s="9"/>
+      <c r="E97" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F97" s="9">
         <v>2</v>
       </c>
@@ -4027,7 +4162,7 @@
       </c>
       <c r="I97" s="20"/>
     </row>
-    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B98" s="9">
         <v>94</v>
       </c>
@@ -4037,7 +4172,9 @@
       <c r="D98" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="E98" s="9"/>
+      <c r="E98" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F98" s="9">
         <v>2</v>
       </c>
@@ -4049,7 +4186,7 @@
       </c>
       <c r="I98" s="20"/>
     </row>
-    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B99" s="9">
         <v>95</v>
       </c>
@@ -4059,7 +4196,9 @@
       <c r="D99" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="E99" s="9"/>
+      <c r="E99" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F99" s="9">
         <v>2</v>
       </c>
@@ -4071,7 +4210,7 @@
       </c>
       <c r="I99" s="20"/>
     </row>
-    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B100" s="9">
         <v>96</v>
       </c>
@@ -4081,7 +4220,9 @@
       <c r="D100" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E100" s="9"/>
+      <c r="E100" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F100" s="9">
         <v>2</v>
       </c>
@@ -4093,7 +4234,7 @@
       </c>
       <c r="I100" s="20"/>
     </row>
-    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B101" s="9">
         <v>97</v>
       </c>
@@ -4103,7 +4244,9 @@
       <c r="D101" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E101" s="9"/>
+      <c r="E101" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F101" s="9">
         <v>2</v>
       </c>
@@ -4115,7 +4258,7 @@
       </c>
       <c r="I101" s="20"/>
     </row>
-    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B102" s="9">
         <v>98</v>
       </c>
@@ -4125,7 +4268,9 @@
       <c r="D102" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="E102" s="9"/>
+      <c r="E102" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F102" s="9">
         <v>2</v>
       </c>
@@ -4137,7 +4282,7 @@
       </c>
       <c r="I102" s="20"/>
     </row>
-    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B103" s="9">
         <v>99</v>
       </c>
@@ -4147,7 +4292,9 @@
       <c r="D103" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="E103" s="9"/>
+      <c r="E103" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F103" s="9">
         <v>2</v>
       </c>
@@ -4159,7 +4306,7 @@
       </c>
       <c r="I103" s="20"/>
     </row>
-    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B104" s="9">
         <v>100</v>
       </c>
@@ -4169,7 +4316,9 @@
       <c r="D104" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="E104" s="9"/>
+      <c r="E104" s="33" t="s">
+        <v>297</v>
+      </c>
       <c r="F104" s="9">
         <v>2</v>
       </c>

--- a/Data/Export/Common/Feature_武将特性.xlsx
+++ b/Data/Export/Common/Feature_武将特性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF5C441-32E9-4C6B-94AC-C1CC1E2C5FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA704EAB-EDAA-4F54-A174-768D59EA5FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="311">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -207,9 +207,6 @@
     <t>掎角</t>
   </si>
   <si>
-    <t>施展齐攻时，让对方陷入混乱</t>
-  </si>
-  <si>
     <t>击破敌方部队时，必定可捕捉无特技「强运」或名马的敌将</t>
   </si>
   <si>
@@ -222,10 +219,6 @@
     <t>掠夺</t>
   </si>
   <si>
-    <t>击破敌方部队时，有机会夺取敌将的道具</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻心</t>
   </si>
   <si>
@@ -270,9 +263,6 @@
   </si>
   <si>
     <t>铁壁</t>
-  </si>
-  <si>
-    <t>就算被一齐攻击，也会视之为一般攻击</t>
   </si>
   <si>
     <t>怒发</t>
@@ -1105,6 +1095,48 @@
   </si>
   <si>
     <t>[{class:"TroopTriggerAction",triggerList:[{class:"TriggerWhenSkillActionEnd"}],actionList:[{class: "TroopSkillBack",condition: {class:"andList",list: [{class: "SkillIsStrategySkill",result: 1},{class: "ProbabilityCheck",probability: 5000}]}}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityImproveResearchCost", value:50}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityChangeSearchingWild", value:100}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"CityChangeFoodCost", value:0, cityKinds:[2,3]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopImproveBuildPower", value:200}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标周围有我方三支部队及以上时，攻击和战法有概率让对方陷入混乱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopTriggerAction", triggerList:[{class:"TriggerWhenSkillAfterHitTroop"}], actionList:[{class:"TroopAddBuff",targetType:1,buffId:1,probability:10000,values:[1,2], weight:[70,30],
+condition:{class:"andList",list:[{class:"TroopAroundTeammateCount",count:3,operator:"gte"} ,{class: "ProbabilityCheck",probability: 5000}] }
+}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopChangeDamage", value:80, isDefender:1}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击损伤减少20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击破敌方部队时，能缴获所有的物资，并有机会夺取敌将的道具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{class:"TroopAddGoldGain", value:100},{class:"TroopAddFoodGain", value:100}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1268,7 +1300,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1368,6 +1400,9 @@
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1737,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>13</v>
@@ -1747,7 +1782,7 @@
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1764,19 +1799,19 @@
         <v>3</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.15">
@@ -1791,7 +1826,7 @@
         <v>15</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F5" s="26">
         <v>4</v>
@@ -1803,7 +1838,7 @@
         <v>16</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.15">
@@ -1818,7 +1853,7 @@
         <v>18</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F6" s="28">
         <v>3</v>
@@ -1830,7 +1865,7 @@
         <v>16</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.15">
@@ -1845,7 +1880,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F7" s="28">
         <v>3</v>
@@ -1857,7 +1892,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="19" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.15">
@@ -1872,7 +1907,7 @@
         <v>22</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F8" s="28">
         <v>2</v>
@@ -1884,7 +1919,7 @@
         <v>16</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.15">
@@ -1899,7 +1934,7 @@
         <v>24</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F9" s="28">
         <v>2</v>
@@ -1911,7 +1946,7 @@
         <v>16</v>
       </c>
       <c r="I9" s="19" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.15">
@@ -1926,7 +1961,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F10" s="28">
         <v>2</v>
@@ -1938,7 +1973,7 @@
         <v>16</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
@@ -1952,7 +1987,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F11" s="9">
         <v>2</v>
@@ -1976,7 +2011,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F12" s="28">
         <v>2</v>
@@ -1988,7 +2023,7 @@
         <v>16</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.15">
@@ -2002,7 +2037,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F13" s="9">
         <v>2</v>
@@ -2026,7 +2061,7 @@
         <v>34</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F14" s="28">
         <v>2</v>
@@ -2038,7 +2073,7 @@
         <v>35</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2052,7 +2087,7 @@
         <v>37</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F15" s="28">
         <v>3</v>
@@ -2064,7 +2099,7 @@
         <v>35</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.15">
@@ -2078,7 +2113,7 @@
         <v>39</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F16" s="11">
         <v>2</v>
@@ -2090,7 +2125,7 @@
         <v>35</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2104,7 +2139,7 @@
         <v>41</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F17" s="28">
         <v>2</v>
@@ -2116,7 +2151,7 @@
         <v>35</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.15">
@@ -2124,13 +2159,13 @@
         <v>14</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>42</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F18" s="11">
         <v>2</v>
@@ -2142,7 +2177,7 @@
         <v>35</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.15">
@@ -2156,7 +2191,7 @@
         <v>44</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F19" s="11">
         <v>2</v>
@@ -2168,7 +2203,7 @@
         <v>35</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2182,7 +2217,7 @@
         <v>46</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F20" s="28">
         <v>2</v>
@@ -2194,7 +2229,7 @@
         <v>35</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2202,13 +2237,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D21" s="28" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F21" s="28">
         <v>2</v>
@@ -2220,7 +2255,7 @@
         <v>48</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2234,7 +2269,7 @@
         <v>50</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F22" s="28">
         <v>3</v>
@@ -2246,10 +2281,10 @@
         <v>35</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.15">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B23" s="11">
         <v>19</v>
       </c>
@@ -2257,10 +2292,10 @@
         <v>51</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>52</v>
+        <v>305</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F23" s="11">
         <v>2</v>
@@ -2270,6 +2305,9 @@
       </c>
       <c r="H23" s="11" t="s">
         <v>35</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2277,13 +2315,13 @@
         <v>20</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F24" s="28">
         <v>2</v>
@@ -2295,7 +2333,7 @@
         <v>35</v>
       </c>
       <c r="I24" s="19" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.15">
@@ -2303,13 +2341,13 @@
         <v>21</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>55</v>
-      </c>
       <c r="E25" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F25" s="11">
         <v>2</v>
@@ -2326,13 +2364,13 @@
         <v>22</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>57</v>
+        <v>309</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F26" s="11">
         <v>2</v>
@@ -2342,6 +2380,9 @@
       </c>
       <c r="H26" s="11" t="s">
         <v>35</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2349,13 +2390,13 @@
         <v>23</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F27" s="28">
         <v>2</v>
@@ -2367,7 +2408,7 @@
         <v>35</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2375,13 +2416,13 @@
         <v>24</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F28" s="28">
         <v>3</v>
@@ -2393,7 +2434,7 @@
         <v>35</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2401,13 +2442,13 @@
         <v>25</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F29" s="28">
         <v>2</v>
@@ -2419,7 +2460,7 @@
         <v>35</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2427,13 +2468,13 @@
         <v>26</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F30" s="28">
         <v>2</v>
@@ -2445,7 +2486,7 @@
         <v>35</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.15">
@@ -2453,13 +2494,13 @@
         <v>27</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F31" s="11">
         <v>2</v>
@@ -2476,13 +2517,13 @@
         <v>28</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F32" s="28">
         <v>2</v>
@@ -2491,10 +2532,10 @@
         <v>3</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2502,13 +2543,13 @@
         <v>29</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F33" s="28">
         <v>2</v>
@@ -2517,10 +2558,10 @@
         <v>3</v>
       </c>
       <c r="H33" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.15">
@@ -2528,13 +2569,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>73</v>
+        <v>308</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F34" s="11">
         <v>2</v>
@@ -2543,7 +2584,10 @@
         <v>3</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.15">
@@ -2551,13 +2595,13 @@
         <v>31</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F35" s="11">
         <v>2</v>
@@ -2566,10 +2610,10 @@
         <v>3</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.15">
@@ -2577,13 +2621,13 @@
         <v>32</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F36" s="11">
         <v>2</v>
@@ -2592,10 +2636,10 @@
         <v>3</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2603,13 +2647,13 @@
         <v>33</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F37" s="28">
         <v>4</v>
@@ -2618,10 +2662,10 @@
         <v>3</v>
       </c>
       <c r="H37" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -2629,13 +2673,13 @@
         <v>34</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F38" s="28">
         <v>2</v>
@@ -2644,10 +2688,10 @@
         <v>3</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I38" s="19" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" spans="2:9" s="15" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -2655,13 +2699,13 @@
         <v>35</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F39" s="14">
         <v>2</v>
@@ -2673,7 +2717,7 @@
         <v>35</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2681,13 +2725,13 @@
         <v>36</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F40" s="14">
         <v>2</v>
@@ -2699,7 +2743,7 @@
         <v>35</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2707,13 +2751,13 @@
         <v>37</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F41" s="14">
         <v>2</v>
@@ -2725,7 +2769,7 @@
         <v>35</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2733,13 +2777,13 @@
         <v>38</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F42" s="14">
         <v>2</v>
@@ -2751,7 +2795,7 @@
         <v>35</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2759,13 +2803,13 @@
         <v>39</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F43" s="14">
         <v>2</v>
@@ -2777,7 +2821,7 @@
         <v>35</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2785,13 +2829,13 @@
         <v>40</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F44" s="14">
         <v>3</v>
@@ -2803,7 +2847,7 @@
         <v>35</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2811,13 +2855,13 @@
         <v>41</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F45" s="14">
         <v>4</v>
@@ -2829,7 +2873,7 @@
         <v>35</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2837,13 +2881,13 @@
         <v>42</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F46" s="14">
         <v>3</v>
@@ -2855,7 +2899,7 @@
         <v>35</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2863,13 +2907,13 @@
         <v>43</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F47" s="14">
         <v>3</v>
@@ -2881,7 +2925,7 @@
         <v>35</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2889,13 +2933,13 @@
         <v>44</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F48" s="14">
         <v>3</v>
@@ -2907,7 +2951,7 @@
         <v>35</v>
       </c>
       <c r="I48" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2915,13 +2959,13 @@
         <v>45</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F49" s="14">
         <v>3</v>
@@ -2933,7 +2977,7 @@
         <v>35</v>
       </c>
       <c r="I49" s="19" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2941,13 +2985,13 @@
         <v>46</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F50" s="14">
         <v>3</v>
@@ -2959,7 +3003,7 @@
         <v>35</v>
       </c>
       <c r="I50" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2967,13 +3011,13 @@
         <v>47</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F51" s="14">
         <v>3</v>
@@ -2985,7 +3029,7 @@
         <v>35</v>
       </c>
       <c r="I51" s="19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -2993,13 +3037,13 @@
         <v>48</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E52" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F52" s="14">
         <v>3</v>
@@ -3011,7 +3055,7 @@
         <v>35</v>
       </c>
       <c r="I52" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3019,13 +3063,13 @@
         <v>49</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F53" s="14">
         <v>4</v>
@@ -3037,7 +3081,7 @@
         <v>35</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="2:9" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3045,13 +3089,13 @@
         <v>50</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F54" s="28">
         <v>3</v>
@@ -3063,7 +3107,7 @@
         <v>35</v>
       </c>
       <c r="I54" s="30" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3071,13 +3115,13 @@
         <v>51</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E55" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F55" s="9">
         <v>2</v>
@@ -3089,7 +3133,7 @@
         <v>35</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="56" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3097,13 +3141,13 @@
         <v>52</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F56" s="9">
         <v>2</v>
@@ -3121,13 +3165,13 @@
         <v>53</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F57" s="11">
         <v>2</v>
@@ -3136,7 +3180,7 @@
         <v>3</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3147,10 +3191,10 @@
         <v>9</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F58" s="28">
         <v>3</v>
@@ -3162,7 +3206,7 @@
         <v>48</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="59" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3170,13 +3214,13 @@
         <v>55</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F59" s="28">
         <v>3</v>
@@ -3188,7 +3232,7 @@
         <v>48</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="60" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3196,13 +3240,13 @@
         <v>56</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F60" s="28">
         <v>3</v>
@@ -3214,7 +3258,7 @@
         <v>48</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3222,13 +3266,13 @@
         <v>57</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F61" s="28">
         <v>3</v>
@@ -3240,7 +3284,7 @@
         <v>48</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="62" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3248,13 +3292,13 @@
         <v>58</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F62" s="28">
         <v>4</v>
@@ -3266,7 +3310,7 @@
         <v>48</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="63" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3274,13 +3318,13 @@
         <v>59</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F63" s="28">
         <v>2</v>
@@ -3292,7 +3336,7 @@
         <v>48</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="64" spans="2:9" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3300,13 +3344,13 @@
         <v>60</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F64" s="28">
         <v>2</v>
@@ -3318,7 +3362,7 @@
         <v>48</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3326,13 +3370,13 @@
         <v>61</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F65" s="28">
         <v>3</v>
@@ -3344,7 +3388,7 @@
         <v>48</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="66" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3352,13 +3396,13 @@
         <v>62</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E66" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F66" s="14">
         <v>4</v>
@@ -3370,10 +3414,10 @@
         <v>48</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="J66" s="15" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="2:10" s="29" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3381,13 +3425,13 @@
         <v>63</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F67" s="28">
         <v>4</v>
@@ -3399,7 +3443,7 @@
         <v>48</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3407,13 +3451,13 @@
         <v>64</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E68" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F68" s="28">
         <v>4</v>
@@ -3425,7 +3469,7 @@
         <v>48</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="69" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3433,13 +3477,13 @@
         <v>65</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F69" s="28">
         <v>4</v>
@@ -3451,7 +3495,7 @@
         <v>48</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="70" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3459,13 +3503,13 @@
         <v>66</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E70" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F70" s="28">
         <v>3</v>
@@ -3477,7 +3521,7 @@
         <v>48</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="2:10" s="29" customFormat="1" ht="270" x14ac:dyDescent="0.15">
@@ -3485,13 +3529,13 @@
         <v>67</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F71" s="28">
         <v>3</v>
@@ -3503,7 +3547,7 @@
         <v>48</v>
       </c>
       <c r="I71" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="72" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3511,13 +3555,13 @@
         <v>68</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F72" s="28">
         <v>3</v>
@@ -3529,7 +3573,7 @@
         <v>48</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.15">
@@ -3537,13 +3581,13 @@
         <v>69</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F73" s="11">
         <v>3</v>
@@ -3555,7 +3599,7 @@
         <v>48</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.15">
@@ -3563,13 +3607,13 @@
         <v>70</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F74" s="11">
         <v>3</v>
@@ -3581,7 +3625,7 @@
         <v>48</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.15">
@@ -3589,13 +3633,13 @@
         <v>71</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F75" s="11">
         <v>3</v>
@@ -3612,13 +3656,13 @@
         <v>72</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F76" s="11">
         <v>4</v>
@@ -3635,13 +3679,13 @@
         <v>73</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F77" s="28">
         <v>2</v>
@@ -3650,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="H77" s="28" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3661,13 +3705,13 @@
         <v>74</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F78" s="28">
         <v>2</v>
@@ -3676,10 +3720,10 @@
         <v>5</v>
       </c>
       <c r="H78" s="28" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="2:10" s="29" customFormat="1" x14ac:dyDescent="0.15">
@@ -3687,13 +3731,13 @@
         <v>75</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F79" s="28">
         <v>3</v>
@@ -3702,10 +3746,10 @@
         <v>5</v>
       </c>
       <c r="H79" s="28" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I79" s="24" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3713,13 +3757,13 @@
         <v>76</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F80" s="14">
         <v>3</v>
@@ -3728,10 +3772,10 @@
         <v>5</v>
       </c>
       <c r="H80" s="14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="81" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3739,13 +3783,13 @@
         <v>77</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E81" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F81" s="14">
         <v>2</v>
@@ -3754,10 +3798,10 @@
         <v>5</v>
       </c>
       <c r="H81" s="14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="82" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3765,13 +3809,13 @@
         <v>78</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F82" s="9">
         <v>2</v>
@@ -3780,22 +3824,24 @@
         <v>5</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="I82" s="20"/>
+        <v>149</v>
+      </c>
+      <c r="I82" s="19" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="83" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B83" s="9">
         <v>79</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F83" s="9">
         <v>2</v>
@@ -3804,34 +3850,36 @@
         <v>7</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="I83" s="20"/>
+        <v>177</v>
+      </c>
+      <c r="I83" s="19" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="84" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B84" s="14">
         <v>80</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F84" s="14">
         <v>2</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H84" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="85" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3839,25 +3887,25 @@
         <v>81</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F85" s="14">
         <v>2</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H85" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3865,25 +3913,25 @@
         <v>82</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E86" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F86" s="14">
         <v>2</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H86" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3894,22 +3942,22 @@
         <v>8</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E87" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F87" s="14">
         <v>2</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H87" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.15">
@@ -3917,25 +3965,25 @@
         <v>84</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F88" s="14">
         <v>2</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H88" s="14" t="s">
         <v>10</v>
       </c>
       <c r="I88" s="19" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -3943,37 +3991,39 @@
         <v>85</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F89" s="9">
         <v>2</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H89" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I89" s="20"/>
+      <c r="I89" s="19" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="90" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B90" s="9">
         <v>86</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F90" s="9">
         <v>2</v>
@@ -3984,20 +4034,22 @@
       <c r="H90" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I90" s="20"/>
+      <c r="I90" s="19" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="91" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B91" s="9">
         <v>87</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F91" s="9">
         <v>2</v>
@@ -4015,13 +4067,13 @@
         <v>88</v>
       </c>
       <c r="C92" s="32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E92" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F92" s="32">
         <v>3</v>
@@ -4030,10 +4082,10 @@
         <v>7</v>
       </c>
       <c r="H92" s="32" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I92" s="19" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="93" spans="2:9" s="33" customFormat="1" x14ac:dyDescent="0.15">
@@ -4041,13 +4093,13 @@
         <v>89</v>
       </c>
       <c r="C93" s="32" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E93" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F93" s="32">
         <v>3</v>
@@ -4056,10 +4108,10 @@
         <v>7</v>
       </c>
       <c r="H93" s="32" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I93" s="19" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -4067,13 +4119,13 @@
         <v>90</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E94" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F94" s="9">
         <v>3</v>
@@ -4082,10 +4134,10 @@
         <v>7</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I94" s="19" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="95" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -4093,13 +4145,13 @@
         <v>91</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E95" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F95" s="9">
         <v>3</v>
@@ -4108,10 +4160,10 @@
         <v>7</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I95" s="19" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="96" spans="2:9" s="10" customFormat="1" x14ac:dyDescent="0.15">
@@ -4119,13 +4171,13 @@
         <v>92</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E96" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F96" s="9">
         <v>2</v>
@@ -4134,7 +4186,7 @@
         <v>8</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I96" s="20"/>
     </row>
@@ -4143,13 +4195,13 @@
         <v>93</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E97" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F97" s="9">
         <v>2</v>
@@ -4158,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I97" s="20"/>
     </row>
@@ -4167,13 +4219,13 @@
         <v>94</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F98" s="9">
         <v>2</v>
@@ -4182,7 +4234,7 @@
         <v>8</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I98" s="20"/>
     </row>
@@ -4191,13 +4243,13 @@
         <v>95</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E99" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F99" s="9">
         <v>2</v>
@@ -4206,7 +4258,7 @@
         <v>8</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I99" s="20"/>
     </row>
@@ -4215,13 +4267,13 @@
         <v>96</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E100" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F100" s="9">
         <v>2</v>
@@ -4230,7 +4282,7 @@
         <v>8</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I100" s="20"/>
     </row>
@@ -4239,13 +4291,13 @@
         <v>97</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E101" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F101" s="9">
         <v>2</v>
@@ -4254,7 +4306,7 @@
         <v>8</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I101" s="20"/>
     </row>
@@ -4263,13 +4315,13 @@
         <v>98</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E102" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F102" s="9">
         <v>2</v>
@@ -4278,7 +4330,7 @@
         <v>8</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I102" s="20"/>
     </row>
@@ -4287,13 +4339,13 @@
         <v>99</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F103" s="9">
         <v>2</v>
@@ -4302,7 +4354,7 @@
         <v>8</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I103" s="20"/>
     </row>
@@ -4311,13 +4363,13 @@
         <v>100</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E104" s="33" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F104" s="9">
         <v>2</v>
@@ -4326,7 +4378,7 @@
         <v>9</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I104" s="20"/>
     </row>
